--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATA\GODOT\MyMod\YukiMod\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D033E1E-503A-42EA-A444-C2AE0DFDD846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321EC754-FA6D-4C5E-84BD-1377CC37EF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -946,7 +946,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CardTable" displayName="CardTable" ref="A1:H91">
   <autoFilter ref="A1:H91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
-    <sortCondition ref="B1:B91"/>
+    <sortCondition ref="C1:C91"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="名称"/>
@@ -1364,29 +1364,29 @@
     </row>
     <row r="4" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
+      <c r="A5" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -1395,44 +1395,44 @@
         <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G5" s="6"/>
-      <c r="H5" s="7">
-        <v>0.54545454545454541</v>
-      </c>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>57</v>
+      <c r="A6" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
+      <c r="H6" s="7">
+        <v>0.54545454545454541</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
@@ -1443,18 +1443,18 @@
       <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>60</v>
+      <c r="E7" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>61</v>
+      <c r="A8" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1465,20 +1465,18 @@
       <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>62</v>
+      <c r="E8" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="H8" s="7">
-        <v>1.3</v>
-      </c>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
@@ -1489,20 +1487,20 @@
       <c r="D9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>64</v>
+      <c r="E9" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="7">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>88</v>
+      <c r="A10" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B10" s="3">
         <v>0</v>
@@ -1511,102 +1509,102 @@
         <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3">
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>104</v>
+        <v>10</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G11" s="6"/>
-      <c r="H11" s="7">
-        <v>0.4</v>
-      </c>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>106</v>
+        <v>28</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="7">
-        <v>0.4</v>
-      </c>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>108</v>
+        <v>28</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G13" s="6"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>177</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>178</v>
+        <v>33</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>23</v>
@@ -1616,75 +1614,75 @@
     </row>
     <row r="15" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>189</v>
+        <v>35</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="7">
-        <v>0.45454545454545447</v>
-      </c>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>199</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>197</v>
+        <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>200</v>
+        <v>28</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>16</v>
+      <c r="A17" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="B17" s="3">
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="7"/>
+      <c r="H17" s="7">
+        <v>1.125</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
@@ -1695,18 +1693,18 @@
       <c r="D18" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>29</v>
+      <c r="E18" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
@@ -1718,19 +1716,19 @@
         <v>28</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="7">
-        <v>0.75</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -1741,18 +1739,18 @@
       <c r="D20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>33</v>
+      <c r="E20" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>34</v>
+      <c r="A21" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -1763,18 +1761,18 @@
       <c r="D21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>35</v>
+      <c r="E21" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>36</v>
+      <c r="A22" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -1785,18 +1783,18 @@
       <c r="D22" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>37</v>
+      <c r="E22" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -1807,20 +1805,18 @@
       <c r="D23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>39</v>
+      <c r="E23" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G23" s="6"/>
-      <c r="H23" s="7">
-        <v>1.125</v>
-      </c>
+      <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>40</v>
+      <c r="A24" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -1831,18 +1827,18 @@
       <c r="D24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>41</v>
+      <c r="E24" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>42</v>
+      <c r="A25" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
@@ -1853,20 +1849,18 @@
       <c r="D25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>43</v>
+      <c r="E25" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>44</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G25" s="6"/>
       <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="B26" s="3">
         <v>1</v>
@@ -1875,20 +1869,20 @@
         <v>27</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B27" s="3">
         <v>1</v>
@@ -1897,20 +1891,22 @@
         <v>27</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G27" s="6"/>
-      <c r="H27" s="7"/>
+      <c r="H27" s="7">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
@@ -1919,20 +1915,22 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="7"/>
+      <c r="H28" s="7">
+        <v>1.175</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>51</v>
+      <c r="A29" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
@@ -1941,20 +1939,20 @@
         <v>27</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>52</v>
+        <v>21</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="7"/>
     </row>
     <row r="30" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>53</v>
+      <c r="A30" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
@@ -1963,20 +1961,22 @@
         <v>27</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G30" s="6"/>
-      <c r="H30" s="7"/>
+      <c r="H30" s="7">
+        <v>0.9555555555555556</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
@@ -1985,20 +1985,22 @@
         <v>27</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G31" s="6"/>
-      <c r="H31" s="7"/>
+      <c r="H31" s="7">
+        <v>1.4222222222222221</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>65</v>
+      <c r="A32" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
@@ -2010,7 +2012,7 @@
         <v>21</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>18</v>
@@ -2019,8 +2021,8 @@
       <c r="H32" s="7"/>
     </row>
     <row r="33" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>67</v>
+      <c r="A33" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="B33" s="3">
         <v>1</v>
@@ -2031,20 +2033,18 @@
       <c r="D33" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>68</v>
+      <c r="E33" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G33" s="6"/>
-      <c r="H33" s="7">
-        <v>0.5</v>
-      </c>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3">
         <v>1</v>
@@ -2056,19 +2056,17 @@
         <v>21</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G34" s="6"/>
-      <c r="H34" s="7">
-        <v>1.175</v>
-      </c>
+      <c r="H34" s="7"/>
     </row>
     <row r="35" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>71</v>
+      <c r="A35" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B35" s="3">
         <v>1</v>
@@ -2076,23 +2074,25 @@
       <c r="C35" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>72</v>
+      <c r="E35" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G35" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="3">
+        <v>86</v>
+      </c>
+      <c r="B36" s="4">
         <v>1</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -2101,20 +2101,16 @@
       <c r="D36" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>74</v>
+      <c r="E36" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="6"/>
-      <c r="H36" s="7">
-        <v>0.9555555555555556</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>75</v>
+      <c r="A37" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="B37" s="3">
         <v>1</v>
@@ -2123,22 +2119,22 @@
         <v>27</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>76</v>
+        <v>10</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="7">
-        <v>1.4222222222222221</v>
+        <v>1.127272727272727</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>77</v>
+      <c r="A38" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
@@ -2147,20 +2143,22 @@
         <v>27</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>78</v>
+        <v>10</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G38" s="6"/>
-      <c r="H38" s="7"/>
+      <c r="H38" s="7">
+        <v>1.0909090909090911</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>79</v>
+      <c r="A39" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
@@ -2169,10 +2167,10 @@
         <v>27</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>80</v>
+        <v>10</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>15</v>
@@ -2182,7 +2180,7 @@
     </row>
     <row r="40" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
@@ -2191,20 +2189,20 @@
         <v>27</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="7"/>
     </row>
     <row r="41" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>83</v>
+      <c r="A41" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B41" s="3">
         <v>1</v>
@@ -2212,103 +2210,105 @@
       <c r="C41" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>84</v>
+      <c r="D41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H41" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="7">
+        <v>0.96103896103896125</v>
+      </c>
     </row>
     <row r="42" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="4">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>87</v>
+        <v>10</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="7"/>
     </row>
     <row r="43" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>91</v>
+        <v>21</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="7">
-        <v>1.127272727272727</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="7">
-        <v>1.0909090909090911</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B45" s="3">
-        <v>1</v>
+      <c r="A45" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" s="4">
+        <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>95</v>
+        <v>21</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>15</v>
@@ -2317,54 +2317,56 @@
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>96</v>
+      <c r="A46" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="B46" s="3">
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>97</v>
+        <v>21</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G46" s="6"/>
-      <c r="H46" s="7"/>
+      <c r="H46" s="7">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="47" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B47" s="3">
         <v>1</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="7">
-        <v>0.96103896103896125</v>
+        <v>1.2222222222222221</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B48" s="3">
         <v>1</v>
@@ -2375,20 +2377,20 @@
       <c r="D48" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>110</v>
+      <c r="E48" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="7">
-        <v>1.4</v>
+        <v>1.377777777777778</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>111</v>
+      <c r="A49" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B49" s="3">
         <v>1</v>
@@ -2400,19 +2402,19 @@
         <v>21</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="7">
-        <v>1.2222222222222221</v>
+        <v>1.1527777777777779</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>113</v>
+      <c r="A50" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
@@ -2424,19 +2426,17 @@
         <v>21</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G50" s="6"/>
-      <c r="H50" s="7">
-        <v>1.377777777777778</v>
-      </c>
+      <c r="H50" s="7"/>
     </row>
     <row r="51" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>115</v>
+      <c r="A51" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
@@ -2448,19 +2448,19 @@
         <v>21</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="7">
-        <v>1.1527777777777779</v>
+        <v>1.4222222222222221</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>117</v>
+      <c r="A52" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
@@ -2471,18 +2471,20 @@
       <c r="D52" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>118</v>
+      <c r="E52" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G52" s="6"/>
-      <c r="H52" s="7"/>
+      <c r="H52" s="7">
+        <v>0.77777777777777779</v>
+      </c>
     </row>
     <row r="53" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>119</v>
+      <c r="A53" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B53" s="3">
         <v>1</v>
@@ -2493,20 +2495,20 @@
       <c r="D53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>120</v>
+      <c r="E53" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="7">
-        <v>1.4222222222222221</v>
+        <v>1.3555555555555561</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>121</v>
+      <c r="A54" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
@@ -2517,20 +2519,20 @@
       <c r="D54" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>122</v>
+      <c r="E54" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="7">
-        <v>0.77777777777777779</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>123</v>
+      <c r="A55" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="B55" s="3">
         <v>1</v>
@@ -2539,22 +2541,22 @@
         <v>103</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>124</v>
+        <v>10</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="7">
-        <v>1.3555555555555561</v>
+        <v>1.2272727272727271</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>125</v>
+      <c r="A56" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
@@ -2563,22 +2565,22 @@
         <v>103</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="7">
-        <v>1.125</v>
+        <v>0.81818181818181812</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
@@ -2590,19 +2592,19 @@
         <v>10</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="7">
-        <v>1.2272727272727271</v>
+        <v>1.081818181818182</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B58" s="3">
         <v>1</v>
@@ -2613,20 +2615,18 @@
       <c r="D58" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>132</v>
+      <c r="E58" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G58" s="6"/>
-      <c r="H58" s="7">
-        <v>0.81818181818181812</v>
-      </c>
+      <c r="H58" s="7"/>
     </row>
     <row r="59" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B59" s="3">
         <v>1</v>
@@ -2638,19 +2638,19 @@
         <v>10</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="7">
-        <v>1.081818181818182</v>
+        <v>0.7272727272727274</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4" t="s">
-        <v>135</v>
+      <c r="A60" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="B60" s="3">
         <v>1</v>
@@ -2662,17 +2662,19 @@
         <v>10</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G60" s="6"/>
-      <c r="H60" s="7"/>
+      <c r="H60" s="7">
+        <v>1.2863636363636359</v>
+      </c>
     </row>
     <row r="61" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B61" s="3">
         <v>1</v>
@@ -2684,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>23</v>
@@ -2695,8 +2697,8 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>139</v>
+      <c r="A62" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="B62" s="3">
         <v>1</v>
@@ -2707,20 +2709,20 @@
       <c r="D62" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>140</v>
+      <c r="E62" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="7">
-        <v>1.2863636363636359</v>
+        <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4" t="s">
-        <v>141</v>
+      <c r="A63" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="B63" s="3">
         <v>1</v>
@@ -2731,20 +2733,20 @@
       <c r="D63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>142</v>
+      <c r="E63" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="7">
-        <v>0.7272727272727274</v>
+        <v>0.94545454545454544</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4" t="s">
-        <v>143</v>
+      <c r="A64" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="B64" s="3">
         <v>1</v>
@@ -2756,19 +2758,19 @@
         <v>10</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="7">
-        <v>0.74545454545454548</v>
+        <v>0.54545454545454541</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>145</v>
+      <c r="A65" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="B65" s="3">
         <v>1</v>
@@ -2780,19 +2782,19 @@
         <v>10</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="7">
-        <v>0.94545454545454544</v>
+        <v>1.272727272727272</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B66" s="3">
         <v>1</v>
@@ -2804,19 +2806,19 @@
         <v>10</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="7">
-        <v>0.54545454545454541</v>
+        <v>0.92045454545454541</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B67" s="3">
         <v>1</v>
@@ -2828,19 +2830,19 @@
         <v>10</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="7">
-        <v>1.272727272727272</v>
+        <v>0.79545454545454541</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>151</v>
+      <c r="A68" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="B68" s="3">
         <v>1</v>
@@ -2851,47 +2853,45 @@
       <c r="D68" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>152</v>
+      <c r="E68" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G68" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>157</v>
+      </c>
       <c r="H68" s="7">
-        <v>0.92045454545454541</v>
+        <v>1.060606060606061</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B69" s="3">
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="B69" s="4">
+        <v>2</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>103</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>154</v>
+        <v>21</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="6"/>
-      <c r="H69" s="7">
-        <v>0.79545454545454541</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
-        <v>155</v>
+      <c r="A70" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>103</v>
@@ -2900,77 +2900,75 @@
         <v>10</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>157</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G70" s="6"/>
       <c r="H70" s="7">
-        <v>1.060606060606061</v>
+        <v>1.363636363636364</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>164</v>
+        <v>232</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>165</v>
+        <v>2</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>233</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G71" s="6"/>
-      <c r="H71" s="7"/>
+      <c r="H71" s="7">
+        <v>1.7636363636363639</v>
+      </c>
     </row>
     <row r="72" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="B72" s="3">
-        <v>1</v>
+        <v>160</v>
+      </c>
+      <c r="B72" s="4">
+        <v>2</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>168</v>
+        <v>10</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G72" s="6"/>
-      <c r="H72" s="7"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="73" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>170</v>
+        <v>10</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>15</v>
@@ -2980,51 +2978,53 @@
     </row>
     <row r="74" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B74" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>165</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
     </row>
     <row r="75" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>173</v>
+      <c r="A75" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>165</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>174</v>
+        <v>10</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G75" s="6"/>
-      <c r="H75" s="7"/>
+      <c r="H75" s="7">
+        <v>0.45454545454545447</v>
+      </c>
     </row>
     <row r="76" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>179</v>
+      <c r="A76" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="B76" s="3">
         <v>1</v>
@@ -3033,10 +3033,10 @@
         <v>165</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>180</v>
+        <v>28</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>18</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="77" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B77" s="3">
         <v>1</v>
@@ -3055,22 +3055,20 @@
         <v>165</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>182</v>
+        <v>28</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G77" s="6"/>
-      <c r="H77" s="7">
-        <v>0.54285714285714293</v>
-      </c>
+      <c r="H77" s="7"/>
     </row>
     <row r="78" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B78" s="3">
         <v>1</v>
@@ -3079,24 +3077,20 @@
         <v>165</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>184</v>
+        <v>28</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>170</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H78" s="7">
-        <v>1.0317460317460321</v>
-      </c>
+      <c r="G78" s="6"/>
+      <c r="H78" s="7"/>
     </row>
     <row r="79" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>186</v>
+      <c r="A79" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="B79" s="3">
         <v>1</v>
@@ -3105,22 +3099,20 @@
         <v>165</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>187</v>
+        <v>28</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G79" s="6"/>
-      <c r="H79" s="7">
-        <v>0.5</v>
-      </c>
+      <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4" t="s">
-        <v>190</v>
+      <c r="A80" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="B80" s="3">
         <v>1</v>
@@ -3129,20 +3121,20 @@
         <v>165</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>28</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>174</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G80" s="6"/>
       <c r="H80" s="7"/>
     </row>
     <row r="81" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4" t="s">
-        <v>192</v>
+      <c r="A81" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="B81" s="3">
         <v>1</v>
@@ -3151,20 +3143,20 @@
         <v>165</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>193</v>
+        <v>21</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G81" s="6"/>
       <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B82" s="3">
         <v>1</v>
@@ -3173,164 +3165,172 @@
         <v>165</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G82" s="6"/>
-      <c r="H82" s="7"/>
+      <c r="H82" s="7">
+        <v>0.54285714285714293</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B83" s="3">
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G83" s="6"/>
-      <c r="H83" s="7"/>
+      <c r="G83" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H83" s="7">
+        <v>1.0317460317460321</v>
+      </c>
     </row>
     <row r="84" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4" t="s">
-        <v>100</v>
+      <c r="A84" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="B84" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>101</v>
+        <v>21</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G84" s="6"/>
-      <c r="H84" s="7"/>
+      <c r="H84" s="7">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="85" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B85" s="4">
-        <v>2</v>
+        <v>190</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>128</v>
+        <v>10</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="G85" s="6"/>
+      <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B86" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G86" s="6"/>
-      <c r="H86" s="7">
-        <v>1.363636363636364</v>
-      </c>
+      <c r="H86" s="7"/>
     </row>
     <row r="87" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="8" t="s">
-        <v>232</v>
+      <c r="A87" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="B87" s="3">
-        <v>2</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>233</v>
+        <v>1</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G87" s="6"/>
-      <c r="H87" s="7">
-        <v>1.7636363636363639</v>
-      </c>
+      <c r="H87" s="7"/>
     </row>
     <row r="88" spans="1:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B88" s="4">
-        <v>2</v>
+        <v>175</v>
+      </c>
+      <c r="B88" s="3">
+        <v>3</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>161</v>
+        <v>28</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>176</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G88" s="6"/>
+      <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="B89" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>103</v>
+        <v>197</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>163</v>
+        <v>21</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>15</v>
@@ -3340,19 +3340,19 @@
     </row>
     <row r="90" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="B90" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>176</v>
+      <c r="E90" s="6" t="s">
+        <v>198</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>15</v>

--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATA\GODOT\MyMod\YukiMod\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321EC754-FA6D-4C5E-84BD-1377CC37EF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071D2190-456B-4898-8F56-99D9969F72DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="239">
   <si>
     <t>名称</t>
   </si>
@@ -497,12 +497,6 @@
   </si>
   <si>
     <t>造成6/9点伤害，下两回合开始时造成6/9点伤害</t>
-  </si>
-  <si>
-    <t>新月</t>
-  </si>
-  <si>
-    <t>造成6点伤害，本回合对其造成伤害为月影增加2/3点伤害。</t>
   </si>
   <si>
     <t>月</t>
@@ -751,6 +745,28 @@
   </si>
   <si>
     <t>对所有敌人造成15/20点伤害；灵感：抽2张牌。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>月读</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>本回合内攻击命中手中月影伤害+2/3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>业火</t>
+  </si>
+  <si>
+    <t>固有，造成5点伤害，你攻击这个目标会时手中月影伤害+1</t>
+  </si>
+  <si>
+    <t>鬼怪狩猎</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成2点伤害3次；凝聚1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -758,7 +774,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -796,6 +812,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFD0D0D0"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -824,7 +847,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -850,6 +873,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -943,10 +970,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CardTable" displayName="CardTable" ref="A1:H91">
-  <autoFilter ref="A1:H91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CardTable" displayName="CardTable" ref="A1:H93">
+  <autoFilter ref="A1:H93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
-    <sortCondition ref="C1:C91"/>
+    <sortCondition descending="1" ref="F1:F91"/>
   </sortState>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="名称"/>
@@ -1341,123 +1368,121 @@
       <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
+      <c r="A3" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="B3" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
+      <c r="A4" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>19</v>
+      <c r="A5" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="7">
-        <v>0.54545454545454541</v>
-      </c>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>57</v>
+      <c r="A7" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="B7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>59</v>
+      <c r="A8" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>27</v>
@@ -1465,270 +1490,264 @@
       <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>60</v>
+      <c r="E8" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7">
-        <v>1.3</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>64</v>
+      <c r="E10" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="7">
-        <v>1</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7">
+        <v>0.92045454545454541</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="7"/>
+      <c r="H12" s="7">
+        <v>0.79545454545454541</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>31</v>
+        <v>187</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="7">
-        <v>0.75</v>
+        <v>0.45454545454545447</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>32</v>
+      <c r="A14" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>33</v>
+      <c r="E14" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>34</v>
+      <c r="A15" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="7"/>
+      <c r="H15" s="7">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="7">
-        <v>1.125</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>40</v>
+      <c r="A18" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="7"/>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>44</v>
-      </c>
+      <c r="G19" s="6"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B20" s="3">
         <v>1</v>
@@ -1739,18 +1758,20 @@
       <c r="D20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>46</v>
+      <c r="E20" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>47</v>
+      <c r="A21" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="B21" s="3">
         <v>1</v>
@@ -1762,17 +1783,17 @@
         <v>28</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>49</v>
+      <c r="A22" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
@@ -1781,20 +1802,20 @@
         <v>27</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>50</v>
+        <v>21</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
@@ -1803,20 +1824,20 @@
         <v>27</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
@@ -1825,20 +1846,20 @@
         <v>27</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>55</v>
+      <c r="A25" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
@@ -1847,352 +1868,364 @@
         <v>27</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>56</v>
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G25" s="6"/>
-      <c r="H25" s="7"/>
+      <c r="H25" s="7">
+        <v>0.96103896103896125</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B26" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>66</v>
+        <v>10</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>67</v>
+      <c r="A27" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>68</v>
+      <c r="E27" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="3">
-        <v>1</v>
+      <c r="A28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="4">
+        <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>70</v>
+      <c r="E28" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="7">
-        <v>1.175</v>
-      </c>
+      <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G29" s="6"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="7">
+        <v>1.4222222222222221</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>74</v>
+      <c r="E30" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="7">
-        <v>0.9555555555555556</v>
+        <v>0.77777777777777779</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="7">
-        <v>1.4222222222222221</v>
+        <v>1.3555555555555561</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G32" s="6"/>
-      <c r="H32" s="7"/>
+      <c r="H32" s="7">
+        <v>0.54545454545454541</v>
+      </c>
     </row>
     <row r="33" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="B33" s="3">
         <v>1</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>80</v>
+        <v>10</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G33" s="6"/>
-      <c r="H33" s="7"/>
+      <c r="H33" s="7">
+        <v>1.272727272727272</v>
+      </c>
     </row>
     <row r="34" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>81</v>
+      <c r="A34" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="B34" s="3">
         <v>1</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>82</v>
+        <v>10</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="7">
+        <v>1.060606060606061</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>83</v>
+      <c r="A35" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>84</v>
+        <v>103</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>85</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G35" s="6"/>
       <c r="H35" s="7"/>
     </row>
     <row r="36" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="4">
+        <v>167</v>
+      </c>
+      <c r="B36" s="3">
         <v>1</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>87</v>
+        <v>28</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="7"/>
     </row>
     <row r="37" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>90</v>
+        <v>169</v>
       </c>
       <c r="B37" s="3">
         <v>1</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G37" s="6"/>
-      <c r="H37" s="7">
-        <v>1.127272727272727</v>
-      </c>
+      <c r="H37" s="7"/>
     </row>
     <row r="38" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="7">
-        <v>1.0909090909090911</v>
+        <v>0.54285714285714293</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>94</v>
+      <c r="A39" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>95</v>
+        <v>21</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G39" s="6"/>
-      <c r="H39" s="7"/>
+      <c r="G39" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H39" s="7">
+        <v>1.0317460317460321</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>96</v>
+      <c r="A40" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>97</v>
+      <c r="E40" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>15</v>
@@ -2202,43 +2235,41 @@
     </row>
     <row r="41" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3">
         <v>1</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G41" s="6"/>
-      <c r="H41" s="7">
-        <v>0.96103896103896125</v>
-      </c>
+      <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="B42" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>101</v>
+        <v>28</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>174</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>15</v>
@@ -2248,339 +2279,325 @@
     </row>
     <row r="43" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>102</v>
+        <v>197</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>104</v>
+        <v>198</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G43" s="6"/>
-      <c r="H43" s="7">
-        <v>0.4</v>
-      </c>
+      <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="B44" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>106</v>
+        <v>196</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G44" s="6"/>
-      <c r="H44" s="7">
-        <v>0.4</v>
-      </c>
+      <c r="H44" s="7"/>
     </row>
     <row r="45" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B45" s="4">
+        <v>19</v>
+      </c>
+      <c r="B45" s="3">
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>108</v>
+      <c r="E45" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G46" s="6"/>
-      <c r="H46" s="7">
-        <v>1.4</v>
-      </c>
+      <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="B47" s="3">
         <v>1</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G47" s="6"/>
-      <c r="H47" s="7">
-        <v>1.2222222222222221</v>
-      </c>
+      <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="B48" s="3">
         <v>1</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>114</v>
+        <v>28</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G48" s="6"/>
-      <c r="H48" s="7">
-        <v>1.377777777777778</v>
-      </c>
+      <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>115</v>
+      <c r="A49" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="B49" s="3">
         <v>1</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G49" s="6"/>
-      <c r="H49" s="7">
-        <v>1.1527777777777779</v>
-      </c>
+      <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3">
         <v>1</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>118</v>
+        <v>28</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G50" s="6"/>
-      <c r="H50" s="7"/>
+      <c r="H50" s="7">
+        <v>1.125</v>
+      </c>
     </row>
     <row r="51" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>120</v>
+        <v>41</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G51" s="6"/>
-      <c r="H51" s="7">
-        <v>1.4222222222222221</v>
-      </c>
+      <c r="H51" s="7"/>
     </row>
     <row r="52" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>121</v>
+      <c r="A52" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>122</v>
+      <c r="E52" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="7">
-        <v>0.77777777777777779</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>123</v>
+      <c r="A53" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="B53" s="3">
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>124</v>
+      <c r="E53" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G53" s="6"/>
-      <c r="H53" s="7">
-        <v>1.3555555555555561</v>
-      </c>
+      <c r="H53" s="7"/>
     </row>
     <row r="54" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>125</v>
+      <c r="A54" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="7">
-        <v>1.125</v>
+        <v>0.9555555555555556</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="B55" s="3">
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="7">
-        <v>1.2272727272727271</v>
+        <v>1.127272727272727</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>132</v>
+      <c r="E56" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="7">
-        <v>0.81818181818181812</v>
+        <v>1.0909090909090911</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
@@ -2589,22 +2606,22 @@
         <v>103</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>134</v>
+        <v>21</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="7">
-        <v>1.081818181818182</v>
+        <v>1.377777777777778</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>135</v>
+      <c r="A58" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B58" s="3">
         <v>1</v>
@@ -2613,20 +2630,22 @@
         <v>103</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G58" s="6"/>
-      <c r="H58" s="7"/>
+      <c r="H58" s="7">
+        <v>1.1527777777777779</v>
+      </c>
     </row>
     <row r="59" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B59" s="3">
         <v>1</v>
@@ -2638,19 +2657,19 @@
         <v>10</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="7">
-        <v>0.7272727272727274</v>
+        <v>1.081818181818182</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>139</v>
+      <c r="A60" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="B60" s="3">
         <v>1</v>
@@ -2662,19 +2681,17 @@
         <v>10</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G60" s="6"/>
-      <c r="H60" s="7">
-        <v>1.2863636363636359</v>
-      </c>
+      <c r="H60" s="7"/>
     </row>
     <row r="61" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B61" s="3">
         <v>1</v>
@@ -2686,7 +2703,7 @@
         <v>10</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>23</v>
@@ -2697,8 +2714,8 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4" t="s">
-        <v>143</v>
+      <c r="A62" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="B62" s="3">
         <v>1</v>
@@ -2709,20 +2726,20 @@
       <c r="D62" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>144</v>
+      <c r="E62" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="7">
-        <v>0.74545454545454548</v>
+        <v>1.2863636363636359</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>145</v>
+      <c r="A63" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="B63" s="3">
         <v>1</v>
@@ -2733,20 +2750,20 @@
       <c r="D63" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>146</v>
+      <c r="E63" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="7">
-        <v>0.94545454545454544</v>
+        <v>0.7272727272727274</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>147</v>
+      <c r="A64" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="B64" s="3">
         <v>1</v>
@@ -2758,22 +2775,22 @@
         <v>10</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="7">
-        <v>0.54545454545454541</v>
+        <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>103</v>
@@ -2781,597 +2798,645 @@
       <c r="D65" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>150</v>
+      <c r="E65" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="7">
-        <v>1.272727272727272</v>
+        <v>1.363636363636364</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>151</v>
+      <c r="A66" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B66" s="3">
-        <v>1</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>103</v>
+        <v>2</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>152</v>
+      <c r="E66" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="7">
-        <v>0.92045454545454541</v>
+        <v>1.7636363636363639</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>154</v>
+        <v>21</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G67" s="6"/>
-      <c r="H67" s="7">
-        <v>0.79545454545454541</v>
-      </c>
+      <c r="H67" s="7"/>
     </row>
     <row r="68" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8" t="s">
-        <v>155</v>
+      <c r="A68" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="B68" s="3">
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>156</v>
+        <v>28</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="H68" s="7">
-        <v>1.060606060606061</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G68" s="6"/>
+      <c r="H68" s="7"/>
     </row>
     <row r="69" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B69" s="4">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>128</v>
+        <v>10</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="G69" s="6"/>
+      <c r="H69" s="7"/>
     </row>
     <row r="70" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4" t="s">
-        <v>158</v>
+      <c r="A70" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B70" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>159</v>
+      <c r="E70" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G70" s="6"/>
       <c r="H70" s="7">
-        <v>1.363636363636364</v>
+        <v>0.54545454545454541</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="s">
-        <v>232</v>
+      <c r="A71" s="4" t="s">
+        <v>57</v>
       </c>
       <c r="B71" s="3">
-        <v>2</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>233</v>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>234</v>
+        <v>21</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G71" s="6"/>
-      <c r="H71" s="7">
-        <v>1.7636363636363639</v>
-      </c>
+      <c r="H71" s="7"/>
     </row>
     <row r="72" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B72" s="4">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>161</v>
+        <v>28</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="G72" s="6"/>
+      <c r="H72" s="7"/>
     </row>
     <row r="73" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="B73" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G73" s="6"/>
-      <c r="H73" s="7"/>
+      <c r="H73" s="7">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="74" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="B74" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>178</v>
+      <c r="E74" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G74" s="6"/>
       <c r="H74" s="7"/>
     </row>
     <row r="75" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4" t="s">
-        <v>188</v>
+      <c r="A75" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="B75" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>189</v>
+        <v>21</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G75" s="6"/>
       <c r="H75" s="7">
-        <v>0.45454545454545447</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
-        <v>164</v>
+      <c r="A76" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B76" s="3">
         <v>1</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>166</v>
+        <v>21</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G76" s="6"/>
-      <c r="H76" s="7"/>
+      <c r="H76" s="7">
+        <v>1.4222222222222221</v>
+      </c>
     </row>
     <row r="77" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4" t="s">
-        <v>167</v>
+      <c r="A77" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="B77" s="3">
         <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>168</v>
+        <v>78</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G77" s="6"/>
       <c r="H77" s="7"/>
     </row>
     <row r="78" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B78" s="3">
+        <v>86</v>
+      </c>
+      <c r="B78" s="4">
         <v>1</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>170</v>
+        <v>21</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="6"/>
-      <c r="H78" s="7"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="79" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>172</v>
+        <v>21</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G79" s="6"/>
-      <c r="H79" s="7"/>
+      <c r="H79" s="7">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="80" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>173</v>
+      <c r="A80" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="B80" s="3">
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>174</v>
+        <v>21</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G80" s="6"/>
-      <c r="H80" s="7"/>
+      <c r="H80" s="7">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="81" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>179</v>
+      <c r="A81" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="B81" s="3">
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>180</v>
+      <c r="E81" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G81" s="6"/>
-      <c r="H81" s="7"/>
+      <c r="H81" s="7">
+        <v>1.2222222222222221</v>
+      </c>
     </row>
     <row r="82" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4" t="s">
-        <v>181</v>
+      <c r="A82" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B82" s="3">
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>182</v>
+      <c r="E82" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G82" s="6"/>
-      <c r="H82" s="7">
-        <v>0.54285714285714293</v>
-      </c>
+      <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="B83" s="3">
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>185</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G83" s="6"/>
       <c r="H83" s="7">
-        <v>1.0317460317460321</v>
+        <v>1.2272727272727271</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>186</v>
+      <c r="A84" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="B84" s="3">
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G84" s="6"/>
       <c r="H84" s="7">
-        <v>0.5</v>
+        <v>0.81818181818181812</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>190</v>
+      <c r="A85" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="B85" s="3">
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="6" t="s">
-        <v>191</v>
+      <c r="E85" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="6"/>
-      <c r="H85" s="7"/>
+      <c r="H85" s="7">
+        <v>0.94545454545454544</v>
+      </c>
     </row>
     <row r="86" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B86" s="3">
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="B86" s="4">
+        <v>2</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>21</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G86" s="6"/>
-      <c r="H86" s="7"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="87" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B87" s="3">
-        <v>1</v>
+        <v>158</v>
+      </c>
+      <c r="B87" s="4">
+        <v>2</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E87" s="6" t="s">
-        <v>195</v>
+      <c r="E87" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" s="6"/>
-      <c r="H87" s="7"/>
+        <v>18</v>
+      </c>
     </row>
     <row r="88" spans="1:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>175</v>
+      <c r="A88" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="B88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>176</v>
+      <c r="E88" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G88" s="6"/>
       <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="4" t="s">
-        <v>199</v>
+      <c r="A89" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="B89" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G89" s="6"/>
       <c r="H89" s="7"/>
     </row>
     <row r="90" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B90" s="3">
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G90" s="6"/>
       <c r="H90" s="7"/>
     </row>
     <row r="91" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="8"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="4"/>
+      <c r="A91" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G91" s="6"/>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="93" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B92" s="10">
+        <v>1</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B93" s="10">
+        <v>1</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="94" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="95" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3482,17 +3547,17 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="whole" allowBlank="1" showDropDown="1" showErrorMessage="1" error="费用列只允许输入数字。" sqref="B2:B91 B93:B201" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="whole" allowBlank="1" showDropDown="1" showErrorMessage="1" error="费用列只允许输入数字。" sqref="B2:B201" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>0</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请输入一个列表中的值" sqref="C2:C91 C93:C201" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请输入一个列表中的值" sqref="C2:C201" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>RarityOptions</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请输入一个列表中的值" sqref="D2:D91 D93:D201" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请输入一个列表中的值" sqref="D2:D201" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>KindOptions</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请输入一个列表中的值" sqref="F2:F91 F93:F201" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="请输入一个列表中的值" sqref="F2:F201" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>FlowOptions</formula1>
     </dataValidation>
   </dataValidations>
@@ -3519,7 +3584,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>20</v>
@@ -3531,16 +3596,16 @@
         <v>27</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>10</v>
@@ -3607,7 +3672,7 @@
       </c>
       <c r="B3" s="4">
         <f>COUNTIF(卡牌表!$F:$F,"*"&amp;$A3&amp;"*")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A3&amp;"*",卡牌表!$C:$C,C$1)</f>
@@ -3619,7 +3684,7 @@
       </c>
       <c r="E3" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A3&amp;"*",卡牌表!$C:$C,E$1)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A3&amp;"*",卡牌表!$C:$C,F$1)</f>
@@ -3639,11 +3704,11 @@
       </c>
       <c r="J3" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A3&amp;"*",卡牌表!$D:$D,J$1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A3&amp;"*",卡牌表!$D:$D,K$1)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A3&amp;"*",卡牌表!$D:$D,L$1)</f>
@@ -3965,10 +4030,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>23</v>
@@ -4078,7 +4143,7 @@
       </c>
       <c r="B4" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A4)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" s="4">
         <v>36</v>
@@ -4089,7 +4154,7 @@
       </c>
       <c r="E4" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A4,卡牌表!$F:$F,"*"&amp;E$1&amp;"*")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A4,卡牌表!$F:$F,"*"&amp;F$1&amp;"*")</f>
@@ -4101,11 +4166,11 @@
       </c>
       <c r="H4" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A4,卡牌表!$D:$D,H$1)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A4,卡牌表!$D:$D,I$1)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A4,卡牌表!$D:$D,J$1)</f>
@@ -4114,7 +4179,7 @@
     </row>
     <row r="5" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A5)</f>
@@ -4194,7 +4259,7 @@
     </row>
     <row r="7" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B7" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A7)</f>
@@ -4234,7 +4299,7 @@
     </row>
     <row r="8" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B8" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A8)</f>
@@ -4486,7 +4551,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>20</v>
@@ -4498,16 +4563,16 @@
         <v>27</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>23</v>
@@ -4528,7 +4593,7 @@
       </c>
       <c r="B2" s="4">
         <f>COUNTIF(卡牌表!$D:$D,$A2)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A2,卡牌表!$C:$C,C$1)</f>
@@ -4540,7 +4605,7 @@
       </c>
       <c r="E2" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A2,卡牌表!$C:$C,E$1)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A2,卡牌表!$C:$C,F$1)</f>
@@ -4564,7 +4629,7 @@
       </c>
       <c r="K2" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A2,卡牌表!$F:$F,"*"&amp;K$1&amp;"*")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A2,卡牌表!$F:$F,"*"&amp;L$1&amp;"*")</f>
@@ -4581,7 +4646,7 @@
       </c>
       <c r="B3" s="4">
         <f>COUNTIF(卡牌表!$D:$D,$A3)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$C:$C,C$1)</f>
@@ -4593,7 +4658,7 @@
       </c>
       <c r="E3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$C:$C,E$1)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$C:$C,F$1)</f>
@@ -4617,7 +4682,7 @@
       </c>
       <c r="K3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$F:$F,"*"&amp;K$1&amp;"*")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$F:$F,"*"&amp;L$1&amp;"*")</f>
@@ -4896,10 +4961,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C1" s="9"/>
     </row>
@@ -4908,7 +4973,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4916,23 +4981,23 @@
         <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4940,23 +5005,23 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4967,21 +5032,21 @@
         <v>143</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
@@ -4989,10 +5054,10 @@
         <v>131</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5201,50 +5266,50 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5252,26 +5317,26 @@
     </row>
     <row r="8" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5524,7 +5589,7 @@
     </row>
     <row r="5" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>15</v>
@@ -5537,12 +5602,12 @@
     </row>
     <row r="7" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DATA\GODOT\MyMod\YukiMod\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071D2190-456B-4898-8F56-99D9969F72DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F97E6-0210-4CBC-82E0-70CB6C2A1990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="17383" windowHeight="10646" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="卡牌表" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="261">
   <si>
     <t>名称</t>
   </si>
@@ -112,9 +112,6 @@
     <t>技能</t>
   </si>
   <si>
-    <t>抽一张（打击以外的）攻击牌；灵感：优先抽取灵感卡。</t>
-  </si>
-  <si>
     <t>灵感</t>
   </si>
   <si>
@@ -268,9 +265,6 @@
     <t>黑云秘技:回转</t>
   </si>
   <si>
-    <t>获得5/8格挡，抽1张牌；灵感：进入黑云姿态。黑云:获得1费</t>
-  </si>
-  <si>
     <t>黑云秘法:降临</t>
   </si>
   <si>
@@ -319,9 +313,6 @@
     <t>冰雪</t>
   </si>
   <si>
-    <t>造成4点伤害2/3次；抽一张有灵感的牌。</t>
-  </si>
-  <si>
     <t>破冰斩</t>
   </si>
   <si>
@@ -337,9 +328,6 @@
     <t>幻变斩</t>
   </si>
   <si>
-    <t>造成3点伤害2/3次，消耗1张手牌，从抽牌堆中选1张牌加入手中。</t>
-  </si>
-  <si>
     <t>斩钢闪</t>
   </si>
   <si>
@@ -400,9 +388,6 @@
     <t>拨日见云</t>
   </si>
   <si>
-    <t>预见3/4，下回合开始时进入黑云姿态并抽1张牌</t>
-  </si>
-  <si>
     <t>人剑合一</t>
   </si>
   <si>
@@ -430,9 +415,6 @@
     <t>黑云秘法:魂佑</t>
   </si>
   <si>
-    <t>获得9/13点格挡，下次进入黑云姿态获得2费</t>
-  </si>
-  <si>
     <t>黑云奥义：灭</t>
   </si>
   <si>
@@ -454,9 +436,6 @@
     <t>迷惑一击</t>
   </si>
   <si>
-    <t>造成4点伤害2次；随机（选择）一张牌触发灵感。</t>
-  </si>
-  <si>
     <t>冰封</t>
   </si>
   <si>
@@ -550,9 +529,6 @@
     <t>满溢</t>
   </si>
   <si>
-    <t>每回合第一次抽满手牌时获得1费。(升级后0费)</t>
-  </si>
-  <si>
     <t>振刀</t>
   </si>
   <si>
@@ -580,9 +556,6 @@
     <t>黑云秘法:出鞘</t>
   </si>
   <si>
-    <t>进入黑云姿态，下次退出黑云姿态时获得一张[纳刀(+)]。</t>
-  </si>
-  <si>
     <t xml:space="preserve">一击必杀！居合抽卡 </t>
   </si>
   <si>
@@ -613,9 +586,6 @@
     <t>黑云奥义：黑雾</t>
   </si>
   <si>
-    <t>造成5/7点伤害；黑云：每有一张技能牌额外攻击一次。</t>
-  </si>
-  <si>
     <t>燕回反</t>
   </si>
   <si>
@@ -640,9 +610,6 @@
     <t>神丶压制准备</t>
   </si>
   <si>
-    <t>抽尽可能多的攻击牌（优先灵感）</t>
-  </si>
-  <si>
     <t>数量</t>
   </si>
   <si>
@@ -686,9 +653,6 @@
   </si>
   <si>
     <t>初始遗物</t>
-  </si>
-  <si>
-    <t>战斗开始时凝聚1。</t>
   </si>
   <si>
     <t>你的月和花获得灵感：抽1张牌，当你同时拥有雪月花时移除3个能力将一张居合加入手牌</t>
@@ -768,6 +732,123 @@
   <si>
     <t>造成2点伤害3次；凝聚1</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>从抽牌堆或弃牌堆抽一张攻击牌（升级后改为抽打击以外的攻击牌）；灵感：优先抽灵感牌。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>从抽牌堆或弃牌堆抽尽可能多的攻击牌（升级后改为抽打击以外的攻击牌）；灵感：优先抽灵感牌。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4点伤害2次；随机（升级后改为选择）一张牌触发灵感。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>预见3/5，下回合开始时进入黑云姿态并抽1张牌。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得9/13点格挡，下次进入黑云姿态时获得2费。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成3点伤害2/3次，消耗1张手牌，抽1张牌。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成4点伤害2/3次；抽一张牌（优先抽灵感牌）。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成7/9点伤害；黑云：每有一张技能牌额外攻击一次。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得5/8格挡，抽一张黑云牌；灵感：进入黑云姿态。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>罕见</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入黑云姿态，下次退出黑云姿态时获得一张[纳刀]/[纳刀+]。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合第一次抽满手牌时获得2费。(升级后0费)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵感</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>月影吊坠</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗开始时，[gold]凝聚[/gold]1。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>月影吊坠+</t>
+  </si>
+  <si>
+    <t>战斗开始时，[gold]凝聚[/gold]2。你的[gold]月影[/gold]费用-1。</t>
+  </si>
+  <si>
+    <t>初始遗物升级</t>
+  </si>
+  <si>
+    <t>黑云戒指</t>
+  </si>
+  <si>
+    <t>战斗开始时，进入[gold]黑云姿态[/gold]。</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>灵感项链</t>
+  </si>
+  <si>
+    <t>每当[gold]灵感[/gold]触发时，对随机敌人造成2点伤害。</t>
+  </si>
+  <si>
+    <t>月影手环</t>
+  </si>
+  <si>
+    <t>回合结束时，若手中有[gold]月影[/gold]，获得2点格挡。</t>
+  </si>
+  <si>
+    <t>灵感冰鞋</t>
+  </si>
+  <si>
+    <t>战斗开始时，手中的[gold]灵感[/gold]牌获得灵感。</t>
+  </si>
+  <si>
+    <t>黑云刀鞘</t>
+  </si>
+  <si>
+    <t>处于[gold]黑云姿态[/gold]时，获得2点力量。</t>
+  </si>
+  <si>
+    <t>月影束带</t>
+  </si>
+  <si>
+    <t>回合结束时，你手中的[gold]月影[/gold]伤害+2。</t>
+  </si>
+  <si>
+    <t>冰雪手镯</t>
+  </si>
+  <si>
+    <t>每回合随机触发一张手牌中的[gold]灵感[/gold]牌。</t>
+  </si>
+  <si>
+    <t>商店</t>
   </si>
 </sst>
 </file>
@@ -1369,19 +1450,19 @@
     </row>
     <row r="3" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>12</v>
@@ -1391,19 +1472,19 @@
     </row>
     <row r="4" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>50</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>12</v>
@@ -1413,19 +1494,19 @@
     </row>
     <row r="5" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>12</v>
@@ -1435,19 +1516,19 @@
     </row>
     <row r="6" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>12</v>
@@ -1457,19 +1538,19 @@
     </row>
     <row r="7" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>12</v>
@@ -1479,19 +1560,19 @@
     </row>
     <row r="8" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>12</v>
@@ -1501,43 +1582,43 @@
     </row>
     <row r="9" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>12</v>
@@ -1561,19 +1642,19 @@
     </row>
     <row r="12" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B12" s="3">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>12</v>
@@ -1585,19 +1666,19 @@
     </row>
     <row r="13" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B13" s="3">
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>12</v>
@@ -1609,19 +1690,19 @@
     </row>
     <row r="14" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B14" s="3">
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>12</v>
@@ -1631,19 +1712,19 @@
     </row>
     <row r="15" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>12</v>
@@ -1677,19 +1758,19 @@
     </row>
     <row r="17" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="3">
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>15</v>
@@ -1701,19 +1782,19 @@
     </row>
     <row r="18" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="3">
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>15</v>
@@ -1725,19 +1806,19 @@
     </row>
     <row r="19" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B19" s="3">
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>15</v>
@@ -1747,43 +1828,43 @@
     </row>
     <row r="20" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="B20" s="3">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>15</v>
@@ -1793,19 +1874,19 @@
     </row>
     <row r="22" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B22" s="3">
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>15</v>
@@ -1815,19 +1896,19 @@
     </row>
     <row r="23" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="3">
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>15</v>
@@ -1837,19 +1918,19 @@
     </row>
     <row r="24" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B24" s="3">
         <v>1</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>15</v>
@@ -1859,19 +1940,19 @@
     </row>
     <row r="25" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>15</v>
@@ -1883,19 +1964,19 @@
     </row>
     <row r="26" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>15</v>
@@ -1905,19 +1986,19 @@
     </row>
     <row r="27" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3">
         <v>0</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>15</v>
@@ -1929,19 +2010,19 @@
     </row>
     <row r="28" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B28" s="4">
         <v>0</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>15</v>
@@ -1951,19 +2032,19 @@
     </row>
     <row r="29" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B29" s="3">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>15</v>
@@ -1975,19 +2056,19 @@
     </row>
     <row r="30" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>15</v>
@@ -1999,19 +2080,19 @@
     </row>
     <row r="31" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B31" s="3">
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>15</v>
@@ -2023,19 +2104,19 @@
     </row>
     <row r="32" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>15</v>
@@ -2047,19 +2128,19 @@
     </row>
     <row r="33" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B33" s="3">
         <v>1</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>15</v>
@@ -2071,25 +2152,25 @@
     </row>
     <row r="34" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B34" s="3">
         <v>1</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H34" s="7">
         <v>1.060606060606061</v>
@@ -2097,19 +2178,19 @@
     </row>
     <row r="35" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B35" s="3">
         <v>3</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>15</v>
@@ -2119,19 +2200,19 @@
     </row>
     <row r="36" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B36" s="3">
         <v>1</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>15</v>
@@ -2141,19 +2222,19 @@
     </row>
     <row r="37" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B37" s="3">
         <v>1</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>15</v>
@@ -2163,19 +2244,19 @@
     </row>
     <row r="38" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>15</v>
@@ -2187,25 +2268,25 @@
     </row>
     <row r="39" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B39" s="3">
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H39" s="7">
         <v>1.0317460317460321</v>
@@ -2213,19 +2294,19 @@
     </row>
     <row r="40" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B40" s="3">
         <v>1</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>15</v>
@@ -2235,19 +2316,19 @@
     </row>
     <row r="41" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="B41" s="3">
         <v>1</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>15</v>
@@ -2257,19 +2338,19 @@
     </row>
     <row r="42" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B42" s="3">
         <v>3</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>15</v>
@@ -2279,41 +2360,41 @@
     </row>
     <row r="43" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>15</v>
+        <v>239</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="7"/>
     </row>
     <row r="44" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B44" s="3">
         <v>1</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>15</v>
@@ -2335,120 +2416,120 @@
         <v>21</v>
       </c>
       <c r="E45" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="7"/>
     </row>
     <row r="46" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="7"/>
     </row>
     <row r="47" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B47" s="3">
-        <v>1</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="F47" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B48" s="3">
-        <v>1</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="F48" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="3">
-        <v>1</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F49" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="3">
-        <v>1</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="F50" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="7">
@@ -2457,44 +2538,44 @@
     </row>
     <row r="51" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="3">
-        <v>1</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="F51" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="7"/>
     </row>
     <row r="52" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="7">
@@ -2503,44 +2584,44 @@
     </row>
     <row r="53" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B53" s="3">
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="7"/>
     </row>
     <row r="54" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B54" s="3">
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="7">
@@ -2549,22 +2630,22 @@
     </row>
     <row r="55" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B55" s="3">
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>91</v>
+        <v>233</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="7">
@@ -2573,22 +2654,22 @@
     </row>
     <row r="56" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="7">
@@ -2597,22 +2678,22 @@
     </row>
     <row r="57" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="7">
@@ -2621,22 +2702,22 @@
     </row>
     <row r="58" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B58" s="3">
         <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="7">
@@ -2645,22 +2726,22 @@
     </row>
     <row r="59" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B59" s="3">
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="7">
@@ -2669,44 +2750,44 @@
     </row>
     <row r="60" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B60" s="3">
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G60" s="6"/>
       <c r="H60" s="7"/>
     </row>
     <row r="61" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B61" s="3">
         <v>1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="7">
@@ -2715,22 +2796,22 @@
     </row>
     <row r="62" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B62" s="3">
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="7">
@@ -2739,22 +2820,22 @@
     </row>
     <row r="63" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B63" s="3">
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="7">
@@ -2763,22 +2844,22 @@
     </row>
     <row r="64" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B64" s="3">
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" s="6"/>
       <c r="H64" s="7">
@@ -2787,22 +2868,22 @@
     </row>
     <row r="65" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B65" s="3">
         <v>2</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G65" s="6"/>
       <c r="H65" s="7">
@@ -2811,22 +2892,22 @@
     </row>
     <row r="66" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B66" s="3">
         <v>2</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G66" s="6"/>
       <c r="H66" s="7">
@@ -2835,44 +2916,44 @@
     </row>
     <row r="67" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B67" s="3">
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G67" s="6"/>
       <c r="H67" s="7"/>
     </row>
     <row r="68" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B68" s="3">
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G68" s="6"/>
       <c r="H68" s="7"/>
@@ -2901,7 +2982,7 @@
     </row>
     <row r="70" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B70" s="3">
         <v>0</v>
@@ -2913,7 +2994,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>18</v>
@@ -2925,19 +3006,19 @@
     </row>
     <row r="71" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71" s="3">
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>18</v>
@@ -2947,19 +3028,19 @@
     </row>
     <row r="72" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B72" s="3">
-        <v>1</v>
-      </c>
-      <c r="C72" s="4" t="s">
+      <c r="D72" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>18</v>
@@ -2969,19 +3050,19 @@
     </row>
     <row r="73" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" s="3">
+        <v>1</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="B73" s="3">
-        <v>1</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>18</v>
@@ -2993,19 +3074,19 @@
     </row>
     <row r="74" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B74" s="3">
         <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>18</v>
@@ -3015,19 +3096,19 @@
     </row>
     <row r="75" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B75" s="3">
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>18</v>
@@ -3039,19 +3120,19 @@
     </row>
     <row r="76" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B76" s="3">
         <v>1</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>18</v>
@@ -3063,19 +3144,19 @@
     </row>
     <row r="77" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B77" s="3">
         <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>18</v>
@@ -3085,19 +3166,19 @@
     </row>
     <row r="78" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B78" s="4">
         <v>1</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>18</v>
@@ -3105,19 +3186,19 @@
     </row>
     <row r="79" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B79" s="3">
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>18</v>
@@ -3129,19 +3210,19 @@
     </row>
     <row r="80" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B80" s="3">
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>18</v>
@@ -3153,19 +3234,19 @@
     </row>
     <row r="81" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B81" s="3">
         <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>18</v>
@@ -3177,19 +3258,19 @@
     </row>
     <row r="82" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B82" s="3">
         <v>1</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>18</v>
@@ -3199,19 +3280,19 @@
     </row>
     <row r="83" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B83" s="3">
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>18</v>
@@ -3223,19 +3304,19 @@
     </row>
     <row r="84" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B84" s="3">
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>18</v>
@@ -3247,19 +3328,19 @@
     </row>
     <row r="85" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B85" s="3">
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>18</v>
@@ -3271,19 +3352,19 @@
     </row>
     <row r="86" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B86" s="4">
         <v>2</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>18</v>
@@ -3291,19 +3372,19 @@
     </row>
     <row r="87" spans="1:8" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B87" s="4">
         <v>2</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>18</v>
@@ -3311,19 +3392,19 @@
     </row>
     <row r="88" spans="1:8" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B88" s="3">
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>18</v>
@@ -3333,19 +3414,19 @@
     </row>
     <row r="89" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B89" s="3">
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>178</v>
+        <v>237</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>18</v>
@@ -3355,19 +3436,19 @@
     </row>
     <row r="90" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B90" s="3">
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>234</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>18</v>
@@ -3377,19 +3458,19 @@
     </row>
     <row r="91" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="11" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B91" s="3">
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>21</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>12</v>
@@ -3399,19 +3480,19 @@
     </row>
     <row r="92" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="11" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B92" s="10">
         <v>1</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F92" s="10" t="s">
         <v>12</v>
@@ -3419,19 +3500,19 @@
     </row>
     <row r="93" spans="1:8" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B93" s="10">
         <v>1</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>10</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>12</v>
@@ -3584,28 +3665,28 @@
         <v>5</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>10</v>
@@ -3614,16 +3695,16 @@
         <v>21</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="4">
         <f>COUNTIF(卡牌表!$F:$F,"*"&amp;$A2&amp;"*")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A2&amp;"*",卡牌表!$C:$C,C$1)</f>
@@ -3647,7 +3728,7 @@
       </c>
       <c r="H2" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A2&amp;"*",卡牌表!$C:$C,H$1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A2&amp;"*",卡牌表!$C:$C,I$1)</f>
@@ -3659,7 +3740,7 @@
       </c>
       <c r="K2" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A2&amp;"*",卡牌表!$D:$D,K$1)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L2" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A2&amp;"*",卡牌表!$D:$D,L$1)</f>
@@ -3770,7 +3851,7 @@
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(卡牌表!$F:$F,"*"&amp;$A5&amp;"*")</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A5&amp;"*",卡牌表!$C:$C,C$1)</f>
@@ -3794,7 +3875,7 @@
       </c>
       <c r="H5" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A5&amp;"*",卡牌表!$C:$C,H$1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A5&amp;"*",卡牌表!$C:$C,I$1)</f>
@@ -3806,7 +3887,7 @@
       </c>
       <c r="K5" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A5&amp;"*",卡牌表!$D:$D,K$1)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="4">
         <f>COUNTIFS(卡牌表!$F:$F,"*"&amp;$A5&amp;"*",卡牌表!$D:$D,L$1)</f>
@@ -4030,13 +4111,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>12</v>
@@ -4054,7 +4135,7 @@
         <v>21</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4099,7 +4180,7 @@
     </row>
     <row r="3" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A3)</f>
@@ -4139,7 +4220,7 @@
     </row>
     <row r="4" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A4)</f>
@@ -4179,7 +4260,7 @@
     </row>
     <row r="5" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B5" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A5)</f>
@@ -4259,7 +4340,7 @@
     </row>
     <row r="7" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B7" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A7)</f>
@@ -4270,7 +4351,7 @@
       </c>
       <c r="D7" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A7,卡牌表!$F:$F,"*"&amp;D$1&amp;"*")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A7,卡牌表!$F:$F,"*"&amp;E$1&amp;"*")</f>
@@ -4282,7 +4363,7 @@
       </c>
       <c r="G7" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A7,卡牌表!$F:$F,"*"&amp;G$1&amp;"*")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A7,卡牌表!$D:$D,H$1)</f>
@@ -4299,7 +4380,7 @@
     </row>
     <row r="8" spans="1:10" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B8" s="4">
         <f>COUNTIF(卡牌表!$C:$C,$A8)</f>
@@ -4551,31 +4632,31 @@
         <v>3</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>12</v>
@@ -4678,7 +4759,7 @@
       </c>
       <c r="J3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$F:$F,"*"&amp;J$1&amp;"*")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$F:$F,"*"&amp;K$1&amp;"*")</f>
@@ -4690,12 +4771,12 @@
       </c>
       <c r="M3" s="4">
         <f>COUNTIFS(卡牌表!$D:$D,$A3,卡牌表!$F:$F,"*"&amp;M$1&amp;"*")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4">
         <f>COUNTIF(卡牌表!$D:$D,$A4)</f>
@@ -4950,7 +5031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R200"/>
+  <dimension ref="A1:R207"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.3046875" style="10" customWidth="1"/>
@@ -4961,19 +5042,19 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="2" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -4981,23 +5062,23 @@
         <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5005,81 +5086,162 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>214</v>
+        <v>241</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="6"/>
-    </row>
-    <row r="10" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>143</v>
+      <c r="A9" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>151</v>
+        <v>246</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>131</v>
+        <v>249</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>251</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="28.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5248,6 +5410,13 @@
     <row r="198" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="199" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="200" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5266,50 +5435,50 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -5317,26 +5486,26 @@
     </row>
     <row r="8" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5562,12 +5731,12 @@
         <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>21</v>
@@ -5578,10 +5747,10 @@
     </row>
     <row r="4" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>18</v>
@@ -5589,7 +5758,7 @@
     </row>
     <row r="5" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>15</v>
@@ -5602,12 +5771,12 @@
     </row>
     <row r="7" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.15" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -99,7 +99,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -129,6 +129,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -282,7 +287,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardTable" displayName="CardTable" ref="A1:H93" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardTable" displayName="CardTable" ref="A1:H95" headerRowCount="1">
   <autoFilter ref="A1:H93"/>
   <sortState ref="A2:H91">
     <sortCondition descending="1" ref="F1:F91"/>
@@ -622,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="20.15234375" customWidth="1" style="10" min="1" max="1"/>
@@ -972,24 +977,44 @@
       </c>
     </row>
     <row r="11" ht="14.15" customHeight="1" s="10">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="n">
-        <v>0.9204545454545454</v>
-      </c>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>咒术</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>升级手中的月影，凝聚1，消耗。（升级后0费）</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>月影</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12" ht="28.3" customHeight="1" s="10">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>月</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>圆舞</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -999,12 +1024,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>造成6/9点伤害，获得月，月影获得2点伤害</t>
+          <t>获得8点格挡，手中月影伤害增加3/5点。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1012,49 +1037,25 @@
           <t>月影</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="n">
-        <v>0.7954545454545454</v>
-      </c>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13" ht="28.3" customHeight="1" s="10">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>影月</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>造成5/10点伤害，这张卡被视为月影；保留；消耗。</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>月影</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="4" t="n"/>
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="7" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.9204545454545454</v>
       </c>
     </row>
     <row r="14" ht="14.15" customHeight="1" s="10">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>上弦之月</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>月</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -1062,49 +1063,51 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>造成6/9点伤害，获得月，月影获得2点伤害</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>月影</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="7" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+    </row>
+    <row r="15" ht="14.15" customHeight="1" s="10">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>影月</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>当释放月影的伤害超过99/66时获得一张居合</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>月影</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="n"/>
-    </row>
-    <row r="15" ht="14.15" customHeight="1" s="10">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>残月</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>凝聚1，手中月影-1费；消耗。（升级后0费）</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>造成5/10点伤害，这张卡被视为月影；保留；消耗。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1114,36 +1117,36 @@
       </c>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="16" ht="28.3" customHeight="1" s="10">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>居合</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>上弦之月</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>对所有敌人造成33/66点+10%当前生命值的伤害，在回合结束时造成33/66+10%已损失生命值的伤害，消耗</t>
+          <t>当释放月影的伤害超过99/66时获得一张居合</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G16" s="6" t="n"/>
@@ -1152,15 +1155,15 @@
     <row r="17" ht="28.3" customHeight="1" s="10">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>红尘</t>
+          <t>残月</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1170,23 +1173,23 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>获得1费，抽2/3张牌，本回合不能再抽牌。</t>
+          <t>凝聚1，手中月影-1费；消耗。（升级后0费）</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" ht="28.3" customHeight="1" s="10">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>背水</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>居合</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -1194,17 +1197,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>Token</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>获得2/3费，本回合不能抽牌。</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>对所有敌人造成50/66点+10%当前生命值的伤害，在回合结束时造成50/66+10%已损失生命值的伤害，消耗</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1213,14 +1216,12 @@
         </is>
       </c>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1" s="10">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>踏前斩</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>红尘</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
@@ -1233,12 +1234,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>造成2/4点伤害，对这回合没被踏前斩命中的敌人释放时返回手牌</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>获得1费，抽2/3张牌，本回合不能再抽牌。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1247,16 +1248,18 @@
         </is>
       </c>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n"/>
+      <c r="H19" s="7" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="20" ht="14.15" customHeight="1" s="10">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>黄昏的羁绊</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>背水</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
@@ -1265,12 +1268,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>固有，不能额外获得费用；回合开始时随机两张卡下次使用前费用减少1。</t>
+          <t>获得2/3费，本回合不能抽牌。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1278,21 +1281,19 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>基础费用按 1 记录；升级后 0 费。</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" ht="28.3" customHeight="1" s="10">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>怒涛斩</t>
+          <t>踏前斩</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1301,12 +1302,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>一回合内打出4/3张攻击牌时抽一张牌</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>造成2/4点伤害，对这回合没被踏前斩命中的敌人释放时返回手牌</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1320,7 +1321,7 @@
     <row r="22" ht="14.15" customHeight="1" s="10">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>起手式</t>
+          <t>黄昏的羁绊</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -1333,12 +1334,12 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>这回合你每打出1张技能牌，下回合内获得1点力量（保留）</t>
+          <t>固有，不能额外获得费用；回合开始时随机两张卡下次使用前费用减少1。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1346,13 +1347,17 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>基础费用按 1 记录；升级后 0 费。</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23" ht="28.3" customHeight="1" s="10">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>看破</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>怒涛斩</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
@@ -1365,12 +1370,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>造成6/9点伤害，从抽牌堆把一张牌放入手中。</t>
+          <t>一回合内打出4/3张攻击牌时抽一张牌</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1382,9 +1387,9 @@
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1" s="10">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>幻变斩</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>起手式</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -1397,12 +1402,12 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>造成3点伤害2/3次，消耗1张手牌，抽1张牌。</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>这回合你每打出1张技能牌，下回合内获得1点力量（保留）</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1414,9 +1419,9 @@
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1" s="10">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>斩钢闪</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>看破</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
@@ -1432,9 +1437,9 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>造成9/12点伤害，连续3回合打出斩钢闪，将一张居合加入手牌</t>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>造成6/9点伤害，从抽牌堆把一张牌放入手中。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1443,18 +1448,16 @@
         </is>
       </c>
       <c r="G25" s="6" t="n"/>
-      <c r="H25" s="7" t="n">
-        <v>0.9610389610389612</v>
-      </c>
+      <c r="H25" s="7" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1" s="10">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>剑舞</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>幻变斩</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
@@ -1466,9 +1469,9 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>造成7/9点伤害，本回合每抽1张牌额外攻击一次（目前增加0）。</t>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>造成3点伤害2/3次，消耗1张手牌，抽1张牌。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1482,25 +1485,25 @@
     <row r="27" ht="14.15" customHeight="1" s="10">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>剑心</t>
+          <t>斩钢闪</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>抽1（保留）。</t>
+          <t>造成9/12点伤害，连续3回合打出斩钢闪，将一张居合加入手牌</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1510,31 +1513,31 @@
       </c>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="7" t="n">
-        <v>0.4</v>
+        <v>0.9610389610389612</v>
       </c>
     </row>
     <row r="28" ht="14.15" customHeight="1" s="10">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>人格切换</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
+          <t>剑舞</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>将2/1张卡放回抽牌堆并抽2张牌</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>造成7/9点伤害，本回合每抽1张牌额外攻击一次（目前增加0）。</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1548,11 +1551,11 @@
     <row r="29" ht="14.15" customHeight="1" s="10">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>人剑合一</t>
+          <t>剑心</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
@@ -1566,7 +1569,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>获得8/11格挡，下两个回合开始时抽1。</t>
+          <t>抽1（保留）。</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1576,17 +1579,17 @@
       </c>
       <c r="G29" s="6" t="n"/>
       <c r="H29" s="7" t="n">
-        <v>1.422222222222222</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" ht="28.3" customHeight="1" s="10">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>回念</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>1</v>
+          <t>人格切换</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -1598,9 +1601,9 @@
           <t>技能</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>获得7/10格挡，从弃牌堆把一张牌放在抽牌堆顶部。</t>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>将2/1张卡放回抽牌堆并抽2张牌</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1609,14 +1612,12 @@
         </is>
       </c>
       <c r="G30" s="6" t="n"/>
-      <c r="H30" s="7" t="n">
-        <v>0.7777777777777778</v>
-      </c>
+      <c r="H30" s="7" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1" s="10">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>未雨绸缪</t>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>人剑合一</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1632,9 +1633,9 @@
           <t>技能</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>获得5/8甲，抽2张牌，先把一张手牌放回抽牌堆底部。</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>获得8/11格挡，下两个回合开始时抽1。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1644,13 +1645,13 @@
       </c>
       <c r="G31" s="6" t="n"/>
       <c r="H31" s="7" t="n">
-        <v>1.355555555555556</v>
+        <v>1.422222222222222</v>
       </c>
     </row>
     <row r="32" ht="14.15" customHeight="1" s="10">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>一式</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>回念</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
@@ -1663,12 +1664,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>造成6/9点伤害 你的下一张攻击牌减少1费</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>获得7/10格挡，从弃牌堆把一张牌放在抽牌堆顶部。</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1678,13 +1679,13 @@
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="33" ht="14.15" customHeight="1" s="10">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>彼岸花</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>未雨绸缪</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -1697,12 +1698,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>造成6/9点伤害，下两回合开始时造成6/9点伤害</t>
+          <t>获得5/8甲，抽2张牌，先把一张手牌放回抽牌堆底部。</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1712,13 +1713,13 @@
       </c>
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="7" t="n">
-        <v>1.272727272727272</v>
+        <v>1.355555555555556</v>
       </c>
     </row>
     <row r="34" ht="14.15" customHeight="1" s="10">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>刀鞘打击</t>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>一式</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
@@ -1734,9 +1735,9 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>造成8/11点伤害，下回合获得1费</t>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>造成6/9点伤害 你的下一张攻击牌减少1费</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1744,23 +1745,19 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>（拥有打击tag）</t>
-        </is>
-      </c>
+      <c r="G34" s="6" t="n"/>
       <c r="H34" s="7" t="n">
-        <v>1.060606060606061</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="35" ht="14.15" customHeight="1" s="10">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>轮回斩</t>
+          <t>彼岸花</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
@@ -1772,9 +1769,9 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>造成5点伤害3/4次，每次抽到时费用-1。</t>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>造成6/9点伤害，下两回合开始时造成6/9点伤害</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1783,12 +1780,14 @@
         </is>
       </c>
       <c r="G35" s="6" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="H35" s="7" t="n">
+        <v>1.272727272727272</v>
+      </c>
     </row>
     <row r="36" ht="14.15" customHeight="1" s="10">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>满溢</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>刀鞘打击</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
@@ -1796,17 +1795,17 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>每回合第一次抽满手牌时获得2费。(升级后0费)</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>造成8/11点伤害，下回合获得1费</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1814,31 +1813,37 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>（拥有打击tag）</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1.060606060606061</v>
+      </c>
     </row>
     <row r="37" ht="14.15" customHeight="1" s="10">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>振刀</t>
+          <t>轮回斩</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>每花费4/3费抽1张牌。</t>
+          <t>造成5点伤害3/4次，每次抽到时费用-1。</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1852,13 +1857,11 @@
     <row r="38" ht="28.3" customHeight="1" s="10">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">一击必杀！居合抽卡 </t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>满溢</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
@@ -1867,12 +1870,12 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>??1???????1??????????????????????1???/??+</t>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>每回合第一次抽满手牌时获得2费。(升级后0费)</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1881,14 +1884,12 @@
         </is>
       </c>
       <c r="G38" s="6" t="n"/>
-      <c r="H38" s="7" t="n">
-        <v>0.5428571428571429</v>
-      </c>
+      <c r="H38" s="7" t="n"/>
     </row>
     <row r="39" ht="14.15" customHeight="1" s="10">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>招架</t>
+          <t>振刀</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -1901,12 +1902,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>获得8/11点防御，如果刚好抵挡全部伤害，下回合开始时获得一张居合</t>
+          <t>每花费4/3费抽1张牌。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1914,23 +1915,19 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>前提是有敌人攻击</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>1.031746031746032</v>
-      </c>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="7" t="n"/>
     </row>
     <row r="40" ht="14.15" customHeight="1" s="10">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>燕回反</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>1</v>
+          <t xml:space="preserve">一击必杀！居合抽卡 </t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
@@ -1939,12 +1936,12 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>释放你上一个释放的攻击，消耗(升级后不消耗)</t>
+          <t>??1???????1??????????????????????1???/??+</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1953,12 +1950,14 @@
         </is>
       </c>
       <c r="G40" s="6" t="n"/>
-      <c r="H40" s="7" t="n"/>
+      <c r="H40" s="7" t="n">
+        <v>0.5428571428571429</v>
+      </c>
     </row>
     <row r="41" ht="14.15" customHeight="1" s="10">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>荣誉</t>
+          <t>招架</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
@@ -1971,12 +1970,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>造成9/12点伤害，如果击杀目标则获得一张居合</t>
+          <t>获得8/11点防御，如果刚好抵挡全部伤害，下回合开始时获得一张居合</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1984,17 +1983,23 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="7" t="n"/>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>前提是有敌人攻击</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>1.031746031746032</v>
+      </c>
     </row>
     <row r="42" ht="14.15" customHeight="1" s="10">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>天刀形态</t>
+          <t>燕回反</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
@@ -2003,12 +2008,12 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>每回合打出的第一张攻击额外打次一次（保留）</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>释放你上一个释放的攻击，消耗(升级后不消耗)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2022,30 +2027,30 @@
     <row r="43" ht="14.15" customHeight="1" s="10">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>神丶压制准备</t>
+          <t>荣誉</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>先古</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>从抽牌堆或弃牌堆抽尽可能多的攻击牌（升级后改为抽打击以外的攻击牌）；灵感：优先抽灵感牌。</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>造成9/12点伤害，如果击杀目标则获得一张居合</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -2054,15 +2059,15 @@
     <row r="44" ht="14.15" customHeight="1" s="10">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>天际斩击</t>
+          <t>天刀形态</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>先古</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2070,9 +2075,9 @@
           <t>能力</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>回合开始时，将手中所有牌放到抽牌堆顶部并抽出。（固有）</t>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>每回合打出的第一张攻击额外打次一次（保留）</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2086,7 +2091,7 @@
     <row r="45" ht="28.3" customHeight="1" s="10">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>压制准备</t>
+          <t>神丶压制准备</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
@@ -2094,7 +2099,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>初始</t>
+          <t>先古</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>从抽牌堆或弃牌堆抽一张攻击牌（升级后改为抽打击以外的攻击牌）；灵感：优先抽灵感牌。</t>
+          <t>从抽牌堆或弃牌堆抽尽可能多的攻击牌（升级后改为抽打击以外的攻击牌）；灵感：优先抽灵感牌。</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2118,30 +2123,30 @@
     <row r="46" ht="14.15" customHeight="1" s="10">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>灵光</t>
+          <t>天际斩击</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>先古</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>触发手牌中灵感效果；消耗（不消耗）。</t>
+          <t>回合开始时，将手中所有牌放到抽牌堆顶部并抽出。（固有）</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G46" s="6" t="n"/>
@@ -2150,25 +2155,25 @@
     <row r="47" ht="28.3" customHeight="1" s="10">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>霜降</t>
+          <t>压制准备</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>初始</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>打击获得灵感:-1费（固有）。</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>从抽牌堆或弃牌堆抽一张攻击牌（升级后改为抽打击以外的攻击牌）；灵感：优先抽灵感牌。</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2182,11 +2187,11 @@
     <row r="48" ht="28.3" customHeight="1" s="10">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>寒霜</t>
+          <t>灵光</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
@@ -2195,12 +2200,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>回合开始时随机触发1/2张手中的灵感。</t>
+          <t>触发手牌中灵感效果；消耗（不消耗）。</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2214,7 +2219,7 @@
     <row r="49" ht="28.3" customHeight="1" s="10">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>冰点之刃</t>
+          <t>霜降</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -2232,7 +2237,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>触发灵感时对随机敌人造成4/6伤害。</t>
+          <t>打击获得灵感:-1费（固有）。</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2244,9 +2249,9 @@
       <c r="H49" s="7" t="n"/>
     </row>
     <row r="50" ht="14.15" customHeight="1" s="10">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>先见之明</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>寒霜</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
@@ -2264,7 +2269,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>回合开始时预见3/4。</t>
+          <t>回合开始时随机触发1/2张手中的灵感。</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2273,14 +2278,12 @@
         </is>
       </c>
       <c r="G50" s="6" t="n"/>
-      <c r="H50" s="7" t="n">
-        <v>1.125</v>
-      </c>
+      <c r="H50" s="7" t="n"/>
     </row>
     <row r="51" ht="14.15" customHeight="1" s="10">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>沉思</t>
+          <t>冰点之刃</t>
         </is>
       </c>
       <c r="B51" s="3" t="n">
@@ -2298,7 +2301,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>使用灵感牌获得2/3格挡。</t>
+          <t>触发灵感时对随机敌人造成4/6伤害。</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2312,7 +2315,7 @@
     <row r="52" ht="14.15" customHeight="1" s="10">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>命定</t>
+          <t>先见之明</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
@@ -2325,12 +2328,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>预见3/4，抽2张牌。</t>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>回合开始时预见3/4。</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2340,13 +2343,13 @@
       </c>
       <c r="G52" s="6" t="n"/>
       <c r="H52" s="7" t="n">
-        <v>1.175</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="53" ht="14.15" customHeight="1" s="10">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>拔刀斩</t>
+          <t>沉思</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
@@ -2359,12 +2362,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>抽1张牌并打出；消耗（升级后不消耗）；灵感:-1费。</t>
+          <t>使用灵感牌获得2/3格挡。</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2376,9 +2379,9 @@
       <c r="H53" s="7" t="n"/>
     </row>
     <row r="54" ht="28.3" customHeight="1" s="10">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>黑云秘技:回转</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>命定</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -2396,7 +2399,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>获得5/8格挡，抽一张黑云牌；灵感：进入黑云姿态。</t>
+          <t>预见3/4，抽2张牌。</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2406,13 +2409,13 @@
       </c>
       <c r="G54" s="6" t="n"/>
       <c r="H54" s="7" t="n">
-        <v>0.9555555555555556</v>
+        <v>1.175</v>
       </c>
     </row>
     <row r="55" ht="28.3" customHeight="1" s="10">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>冰雪</t>
+          <t>拔刀斩</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
@@ -2425,12 +2428,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>造成4点伤害2/3次；抽一张牌（优先抽灵感牌）。</t>
+          <t>抽1张牌并打出；消耗（升级后不消耗）；灵感:-1费。</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2439,14 +2442,12 @@
         </is>
       </c>
       <c r="G55" s="6" t="n"/>
-      <c r="H55" s="7" t="n">
-        <v>1.127272727272727</v>
-      </c>
+      <c r="H55" s="7" t="n"/>
     </row>
     <row r="56" ht="14.15" customHeight="1" s="10">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>破冰斩</t>
+          <t>黑云秘技:回转</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
@@ -2459,12 +2460,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>对所有敌人造成8/10点伤害；灵感：额外攻击一次。</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>获得5/8格挡，抽一张黑云牌；灵感：进入黑云姿态。</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2474,13 +2475,13 @@
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="7" t="n">
-        <v>1.090909090909091</v>
+        <v>0.9555555555555556</v>
       </c>
     </row>
     <row r="57" ht="14.15" customHeight="1" s="10">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>寒冰庇护</t>
+          <t>冰雪</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
@@ -2488,17 +2489,17 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>获得7/10点格挡，抽1；灵感：抽1。</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>造成4点伤害2/3次；抽一张牌（优先抽灵感牌）。</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2508,13 +2509,13 @@
       </c>
       <c r="G57" s="6" t="n"/>
       <c r="H57" s="7" t="n">
-        <v>1.377777777777778</v>
+        <v>1.127272727272727</v>
       </c>
     </row>
     <row r="58" ht="14.15" customHeight="1" s="10">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>天眼</t>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>破冰斩</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
@@ -2522,17 +2523,17 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>7/9甲，预见3/5。</t>
+          <t>对所有敌人造成8/10点伤害；灵感：额外攻击一次。</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2542,13 +2543,13 @@
       </c>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="7" t="n">
-        <v>1.152777777777778</v>
+        <v>1.090909090909091</v>
       </c>
     </row>
     <row r="59" ht="28.3" customHeight="1" s="10">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>严寒</t>
+          <t>寒冰庇护</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
@@ -2561,12 +2562,12 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>造成5点伤害，抽1/2张牌；灵感：额外造成5点伤害。</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>获得7/10点格挡，抽1；灵感：抽1。</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2576,13 +2577,13 @@
       </c>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="7" t="n">
-        <v>1.081818181818182</v>
+        <v>1.377777777777778</v>
       </c>
     </row>
     <row r="60" ht="28.3" customHeight="1" s="10">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>迷惑一击</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>天眼</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
@@ -2595,12 +2596,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>造成4点伤害2次；随机（升级后改为选择）一张牌触发灵感。</t>
+          <t>7/9甲，预见3/5。</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2609,12 +2610,14 @@
         </is>
       </c>
       <c r="G60" s="6" t="n"/>
-      <c r="H60" s="7" t="n"/>
+      <c r="H60" s="7" t="n">
+        <v>1.152777777777778</v>
+      </c>
     </row>
     <row r="61" ht="28.3" customHeight="1" s="10">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>冰封</t>
+          <t>严寒</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
@@ -2632,7 +2635,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>造成8/11伤害，施加1虚弱；灵感：施加2虚弱。</t>
+          <t>造成5点伤害，抽1/2张牌；灵感：额外造成5点伤害。</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2642,13 +2645,13 @@
       </c>
       <c r="G61" s="6" t="n"/>
       <c r="H61" s="7" t="n">
-        <v>0.7272727272727274</v>
+        <v>1.081818181818182</v>
       </c>
     </row>
     <row r="62" ht="28.3" customHeight="1" s="10">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>斩破命运</t>
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>迷惑一击</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
@@ -2666,7 +2669,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>打7/9，预见2/3，抽1。</t>
+          <t>造成8点伤害；随机（升级后改为选择）一张牌触发灵感。</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2675,14 +2678,12 @@
         </is>
       </c>
       <c r="G62" s="6" t="n"/>
-      <c r="H62" s="7" t="n">
-        <v>1.286363636363636</v>
-      </c>
+      <c r="H62" s="7" t="n"/>
     </row>
     <row r="63" ht="14.15" customHeight="1" s="10">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>快速斩</t>
+          <t>冰封</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
@@ -2700,7 +2701,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>造成2点伤害3次；灵感：额外攻击2次。</t>
+          <t>造成8/11伤害，施加1虚弱；灵感：施加2虚弱。</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2714,9 +2715,9 @@
       </c>
     </row>
     <row r="64" ht="28.3" customHeight="1" s="10">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>雪</t>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>斩破命运</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
@@ -2732,9 +2733,9 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>造成6/9点伤害，获得雪，灵感:抽一张牌</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>打7/9，预见2/3，抽1。</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2744,17 +2745,17 @@
       </c>
       <c r="G64" s="6" t="n"/>
       <c r="H64" s="7" t="n">
-        <v>0.7454545454545455</v>
+        <v>1.286363636363636</v>
       </c>
     </row>
     <row r="65" ht="28.3" customHeight="1" s="10">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>偷袭斩</t>
+          <t>快速斩</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
@@ -2768,7 +2769,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>对所有敌人造成15点伤害；灵感：减少1/2费。</t>
+          <t>造成2点伤害3次；灵感：额外攻击2次。</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2778,19 +2779,19 @@
       </c>
       <c r="G65" s="6" t="n"/>
       <c r="H65" s="7" t="n">
-        <v>1.363636363636364</v>
+        <v>0.7272727272727274</v>
       </c>
     </row>
     <row r="66" ht="28.3" customHeight="1" s="10">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>高速斩击</t>
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>雪</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
@@ -2800,9 +2801,9 @@
           <t>攻击</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>对所有敌人造成15/20点伤害；灵感：抽2张牌。</t>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>造成6/9点伤害，获得雪，灵感:抽一张牌</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2812,31 +2813,31 @@
       </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="7" t="n">
-        <v>1.763636363636364</v>
+        <v>0.7454545454545455</v>
       </c>
     </row>
     <row r="67" ht="14.15" customHeight="1" s="10">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>天际</t>
+          <t>偷袭斩</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>把手牌放到抽牌堆顶部，并抽同等数量的卡；消耗（不消耗）。</t>
+          <t>对所有敌人造成15点伤害；灵感：减少1/2费。</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2845,30 +2846,32 @@
         </is>
       </c>
       <c r="G67" s="6" t="n"/>
-      <c r="H67" s="7" t="n"/>
+      <c r="H67" s="7" t="n">
+        <v>1.363636363636364</v>
+      </c>
     </row>
     <row r="68" ht="28.3" customHeight="1" s="10">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>零度</t>
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>高速斩击</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
+        <v>2</v>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>通常</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>当释放33/22次灵感牌，获得一张居合</t>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>对所有敌人造成15/20点伤害；灵感：抽2张牌。</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2877,96 +2880,96 @@
         </is>
       </c>
       <c r="G68" s="6" t="n"/>
-      <c r="H68" s="7" t="n"/>
+      <c r="H68" s="7" t="n">
+        <v>1.763636363636364</v>
+      </c>
     </row>
     <row r="69" ht="14.15" customHeight="1" s="10">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>纳刀</t>
+          <t>天际</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>造成5/7点伤害，本回合每释放一张攻击牌额外攻击一次；手里没有攻击牌时费用-1；消耗。</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>把手牌放到抽牌堆顶部，并抽同等数量的卡；消耗（不消耗）。</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G69" s="6" t="n"/>
       <c r="H69" s="7" t="n"/>
     </row>
     <row r="70" ht="28.3" customHeight="1" s="10">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>黑云奥义:拔刀</t>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>零度</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>初始</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>造成4/6点伤害；黑云：额外攻击一次。</t>
+          <t>当释放33/22次灵感牌，获得一张居合</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G70" s="6" t="n"/>
-      <c r="H70" s="7" t="n">
-        <v>0.5454545454545454</v>
-      </c>
+      <c r="H70" s="7" t="n"/>
     </row>
     <row r="71" ht="28.3" customHeight="1" s="10">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>黑云秘法:燕回</t>
+          <t>纳刀</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>Token</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>把随机一张黑云牌从抽牌堆或弃牌堆移至手牌；黑云：保留黑云姿态。消耗（不再消耗）</t>
+          <t>造成5/7点伤害，本回合每释放一张攻击牌额外攻击一次；手里没有攻击牌时费用-1；消耗。</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2978,27 +2981,27 @@
       <c r="H71" s="7" t="n"/>
     </row>
     <row r="72" ht="14.15" customHeight="1" s="10">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>如影随形</t>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>黑云奥义:拔刀</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>初始</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>回合开始时若在黑云姿态则抽一张牌，优先黑云牌。(固有)</t>
+          <t>造成4/6点伤害；黑云：额外攻击一次。</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3007,16 +3010,18 @@
         </is>
       </c>
       <c r="G72" s="6" t="n"/>
-      <c r="H72" s="7" t="n"/>
+      <c r="H72" s="7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
     </row>
     <row r="73" ht="14.15" customHeight="1" s="10">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>引雷天云</t>
+          <t>黑云秘法:燕回</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
@@ -3025,12 +3030,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>黑云姿态下获得3/4力量。</t>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>把随机一张黑云牌从抽牌堆或弃牌堆移至手牌；黑云：保留黑云姿态。消耗（不再消耗）</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3039,14 +3044,12 @@
         </is>
       </c>
       <c r="G73" s="6" t="n"/>
-      <c r="H73" s="7" t="n">
-        <v>0.75</v>
-      </c>
+      <c r="H73" s="7" t="n"/>
     </row>
     <row r="74" ht="14.15" customHeight="1" s="10">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>黑云秘法:霞阵</t>
+          <t>如影随形</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
@@ -3059,12 +3062,12 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>抽1张牌，这张牌下次使用费用减少1；黑云：保留黑云姿态。(保留)</t>
+          <t>回合开始时若在黑云姿态则抽一张牌，优先黑云牌。(固有)</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3076,9 +3079,9 @@
       <c r="H74" s="7" t="n"/>
     </row>
     <row r="75" ht="14.15" customHeight="1" s="10">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>黑云心法</t>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>引雷天云</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
@@ -3091,12 +3094,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>一回合内保留黑云姿态；黑云：本回合内获得2/3力量。</t>
+          <t>能力</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>黑云姿态下获得3/4力量。</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3106,13 +3109,13 @@
       </c>
       <c r="G75" s="6" t="n"/>
       <c r="H75" s="7" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="76" ht="28.3" customHeight="1" s="10">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>黑云秘法:降临</t>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>黑云秘法:霞阵</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
@@ -3130,7 +3133,7 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>获得8/11格挡，下次进入黑云姿态时为所有敌方施加1层易伤</t>
+          <t>抽1张牌，这张牌下次使用费用减少1；黑云：保留黑云姿态。(保留)</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3139,118 +3142,120 @@
         </is>
       </c>
       <c r="G76" s="6" t="n"/>
-      <c r="H76" s="7" t="n">
-        <v>1.422222222222222</v>
-      </c>
+      <c r="H76" s="7" t="n"/>
     </row>
     <row r="77" ht="28.3" customHeight="1" s="10">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>黑云心法</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>一回合内保留黑云姿态；黑云：本回合内获得2/3力量。</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>黑云</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="7" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" ht="14.15" customHeight="1" s="10">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>黑云秘法:降临</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>获得8/11格挡，下次进入黑云姿态时为所有敌方施加1层易伤</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>黑云</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="7" t="n">
+        <v>1.422222222222222</v>
+      </c>
+    </row>
+    <row r="79" ht="14.15" customHeight="1" s="10">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
           <t>黑云秘法:虚像</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="B79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>施加2/3层虚弱，下回合进入黑云姿态</t>
         </is>
       </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>黑云</t>
         </is>
       </c>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="7" t="n"/>
-    </row>
-    <row r="78" ht="14.15" customHeight="1" s="10">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>黑云秘法:幕临</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>罕见</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>获得7/10点格挡，下次进入黑云姿态的回合内获得3点力量</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>黑云</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="14.15" customHeight="1" s="10">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>黑云奥义：残</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>通常</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>抽一张牌；黑云：保留黑云姿态。消耗（不再消耗）</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>黑云</t>
-        </is>
-      </c>
       <c r="G79" s="6" t="n"/>
-      <c r="H79" s="7" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="H79" s="7" t="n"/>
     </row>
     <row r="80" ht="28.3" customHeight="1" s="10">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>黑云秘法:隼舞</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
+          <t>黑云秘法:幕临</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -3258,29 +3263,25 @@
           <t>技能</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>获得9/12点格挡；黑云：抽2张牌。</t>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>获得7/10点格挡，下次进入黑云姿态的回合内获得3点力量</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>黑云</t>
         </is>
-      </c>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="7" t="n">
-        <v>1.4</v>
       </c>
     </row>
     <row r="81" ht="14.15" customHeight="1" s="10">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>黑云秘法:积雨</t>
+          <t>黑云奥义：残</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
@@ -3292,9 +3293,9 @@
           <t>技能</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>获得8/11格挡，下回合开始时进入黑云姿态</t>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>抽一张牌；黑云：保留黑云姿态。消耗（不再消耗）</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3304,13 +3305,13 @@
       </c>
       <c r="G81" s="6" t="n"/>
       <c r="H81" s="7" t="n">
-        <v>1.222222222222222</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="82" ht="14.15" customHeight="1" s="10">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>拨日见云</t>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>黑云秘法:隼舞</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
@@ -3326,9 +3327,9 @@
           <t>技能</t>
         </is>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>预见3/5，下回合开始时进入黑云姿态并抽1张牌。</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>获得9/12点格挡；黑云：抽2张牌。</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3337,12 +3338,14 @@
         </is>
       </c>
       <c r="G82" s="6" t="n"/>
-      <c r="H82" s="7" t="n"/>
+      <c r="H82" s="7" t="n">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="83" ht="14.15" customHeight="1" s="10">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>黑云奥义：灭</t>
+          <t>黑云秘法:积雨</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
@@ -3355,12 +3358,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>造成9/12点伤害；黑云：额外攻击一次。</t>
+          <t>获得8/11格挡，下回合开始时进入黑云姿态</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3370,13 +3373,13 @@
       </c>
       <c r="G83" s="6" t="n"/>
       <c r="H83" s="7" t="n">
-        <v>1.227272727272727</v>
+        <v>1.222222222222222</v>
       </c>
     </row>
     <row r="84" ht="14.15" customHeight="1" s="10">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>花</t>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>拨日见云</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
@@ -3389,46 +3392,44 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>预见3/5，下回合开始时进入黑云姿态并抽1张牌。</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>黑云</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="7" t="n"/>
+    </row>
+    <row r="85" ht="14.15" customHeight="1" s="10">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>黑云奥义：灭</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>造成6/9点伤害，获得花，黑云：额外攻击一次</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>黑云</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="n"/>
-      <c r="H84" s="7" t="n">
-        <v>0.8181818181818181</v>
-      </c>
-    </row>
-    <row r="85" ht="14.15" customHeight="1" s="10">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>黑云奥义:殇</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>通常</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>造成9/12点伤害，黑云：施加2层易伤</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>造成9/12点伤害；黑云：额外攻击一次。</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3438,155 +3439,159 @@
       </c>
       <c r="G85" s="6" t="n"/>
       <c r="H85" s="7" t="n">
-        <v>0.9454545454545454</v>
+        <v>1.227272727272727</v>
       </c>
     </row>
     <row r="86" ht="14.15" customHeight="1" s="10">
       <c r="A86" s="4" t="inlineStr">
         <is>
+          <t>花</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>造成6/9点伤害，获得花，黑云：额外攻击一次</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>黑云</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="n"/>
+      <c r="H86" s="7" t="n">
+        <v>0.8181818181818181</v>
+      </c>
+    </row>
+    <row r="87" ht="28.3" customHeight="1" s="10">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>黑云奥义:殇</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>通常</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>造成9/12点伤害，黑云：施加2层易伤</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>黑云</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="7" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+    </row>
+    <row r="88" ht="42.45" customHeight="1" s="10">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
           <t>黑云秘法:魂佑</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n">
+      <c r="B88" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>技能</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>获得9/13点格挡，下次进入黑云姿态时获得2费。</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>黑云</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="28.3" customHeight="1" s="10">
-      <c r="A87" s="4" t="inlineStr">
+    <row r="89" ht="14.15" customHeight="1" s="10">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>黑云秘法:影缚</t>
         </is>
       </c>
-      <c r="B87" s="4" t="n">
+      <c r="B89" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>造成4点伤害3/4次，下次进入黑云姿态抽3张牌</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>黑云</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="42.45" customHeight="1" s="10">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="90" ht="14.15" customHeight="1" s="10">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>黑雾降临</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="B90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>能力</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>回合开始时进入黑云姿态（固有）。</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>黑云</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="7" t="n"/>
-    </row>
-    <row r="89" ht="14.15" customHeight="1" s="10">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>黑云秘法:出鞘</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>进入黑云姿态，下次退出黑云姿态时获得一张[纳刀]/[纳刀+]。</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>黑云</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="7" t="n"/>
-    </row>
-    <row r="90" ht="14.15" customHeight="1" s="10">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>黑云奥义：黑雾</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>造成7/9点伤害；黑云：每有一张技能牌额外攻击一次。</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3598,17 +3603,17 @@
       <c r="H90" s="7" t="n"/>
     </row>
     <row r="91" ht="14.15" customHeight="1" s="10">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>月读</t>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>黑云秘法:出鞘</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3616,81 +3621,143 @@
           <t>技能</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>本回合内攻击命中手中月影伤害+2/3</t>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>进入黑云姿态，下次退出黑云姿态时获得一张[纳刀]/[纳刀+]。</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G91" s="6" t="n"/>
       <c r="H91" s="7" t="n"/>
     </row>
     <row r="92" ht="14.15" customHeight="1" s="10">
-      <c r="A92" s="11" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>黑云奥义：黑雾</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>造成7/9点伤害；黑云：每有一张技能牌额外攻击一次。</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>黑云</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="n"/>
+      <c r="H92" s="7" t="n"/>
+    </row>
+    <row r="93" ht="14.15" customHeight="1" s="10">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>月读</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>本回合内攻击命中手中月影伤害+2/3</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>月影</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="7" t="n"/>
+    </row>
+    <row r="94" ht="14.15" customHeight="1" s="10">
+      <c r="A94" s="11" t="inlineStr">
         <is>
           <t>业火</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B94" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D94" s="0" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="E92" s="11" t="inlineStr">
+      <c r="E94" s="11" t="inlineStr">
         <is>
           <t>固有，造成5点伤害，你攻击这个目标会时手中月影伤害+1</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F94" s="0" t="inlineStr">
         <is>
           <t>月影</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="14.15" customHeight="1" s="10">
-      <c r="A93" s="12" t="inlineStr">
+    <row r="95" ht="14.15" customHeight="1" s="10">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>鬼怪狩猎</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="inlineStr">
+      <c r="B95" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D95" s="0" t="inlineStr">
         <is>
           <t>攻击</t>
         </is>
       </c>
-      <c r="E93" s="12" t="inlineStr">
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>造成2点伤害3次；凝聚1</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F95" s="0" t="inlineStr">
         <is>
           <t>月影</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="14.15" customHeight="1" s="10"/>
-    <row r="95" ht="14.15" customHeight="1" s="10"/>
     <row r="96" ht="14.15" customHeight="1" s="10"/>
     <row r="97" ht="14.15" customHeight="1" s="10"/>
     <row r="98" ht="14.15" customHeight="1" s="10"/>
@@ -4420,7 +4487,7 @@
         <v/>
       </c>
       <c r="C3" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="4">
         <f>COUNTIFS(卡牌表!$C:$C,$A3,卡牌表!$F:$F,"*"&amp;D$1&amp;"*")</f>
@@ -5417,14 +5484,14 @@
           <t>战斗开始时，[gold]凝聚[/gold]1。</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>初始遗物</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14.15" customHeight="1" s="10">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>月影吊坠+</t>
         </is>
@@ -5434,14 +5501,14 @@
           <t>战斗开始时，[gold]凝聚[/gold]2。你的[gold]月影[/gold]费用-1。</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>初始遗物升级</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14.15" customHeight="1" s="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>黑云戒指</t>
         </is>
@@ -5451,14 +5518,14 @@
           <t>战斗开始时，进入[gold]黑云姿态[/gold]。</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14.15" customHeight="1" s="10">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>灵感项链</t>
         </is>
@@ -5468,14 +5535,14 @@
           <t>每当[gold]灵感[/gold]触发时，对随机敌人造成2点伤害。</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14.15" customHeight="1" s="10">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>月影手环</t>
         </is>
@@ -5485,14 +5552,14 @@
           <t>回合结束时，若手中有[gold]月影[/gold]，获得2点格挡。</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>罕见</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14.15" customHeight="1" s="10">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>灵感冰鞋</t>
         </is>
@@ -5502,14 +5569,14 @@
           <t>战斗开始时，手中的[gold]灵感[/gold]牌获得灵感。</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14.15" customHeight="1" s="10">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>黑云刀鞘</t>
         </is>
@@ -5519,14 +5586,14 @@
           <t>处于[gold]黑云姿态[/gold]时，获得2点力量。</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14.15" customHeight="1" s="10">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>月影束带</t>
         </is>
@@ -5536,14 +5603,14 @@
           <t>回合结束时，你手中的[gold]月影[/gold]伤害+2。</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>稀有</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1" s="10">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>冰雪手镯</t>
         </is>
@@ -5553,7 +5620,7 @@
           <t>每回合随机触发一张手牌中的[gold]灵感[/gold]牌。</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>商店</t>
         </is>

--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卡牌表" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,34 +22,23 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'说明'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'关键词，能力与遗物'!$A$1:$C$5</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,7 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,18 +64,17 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </left>
       <right style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </right>
       <top style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -101,7 +90,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -465,7 +454,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H104"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -666,11 +655,11 @@
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>严寒</t>
+          <t>偷袭斩</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -684,7 +673,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>造成5/8点伤害。；抽1张牌。；灵感：额外释放1次。</t>
+          <t>对所有敌人造成15点伤害。；灵感：这张牌费用减少1/2。</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -694,7 +683,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YAN_HAN；类: YanHan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TOU_XI_ZHAN；类: TouXiZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
@@ -702,11 +691,11 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>偷袭斩</t>
+          <t>冰封</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -720,7 +709,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成15点伤害。；灵感：这张牌费用减少1/2。</t>
+          <t>造成8/11点伤害。；施加1层虚弱。；灵感：额外打出1次。</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -730,7 +719,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TOU_XI_ZHAN；类: TouXiZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BING_FENG；类: BingFeng；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H7" s="2" t="n"/>
@@ -738,7 +727,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>冰封</t>
+          <t>快速斩</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -756,7 +745,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>造成8/11点伤害。；施加1层虚弱。；灵感：额外打出1次。</t>
+          <t>造成2/3点伤害3次。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -766,7 +755,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BING_FENG；类: BingFeng；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-KUAI_SU_ZHAN；类: KuaiSuZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H8" s="2" t="n"/>
@@ -774,7 +763,7 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>快速斩</t>
+          <t>斩破命运</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -792,7 +781,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>造成2/3点伤害3次。；灵感：这张牌费用减少1。</t>
+          <t>造成7/9点伤害。；预见2/3。；抽1张牌。</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -802,7 +791,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-KUAI_SU_ZHAN；类: KuaiSuZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-ZHAN_PO_MING_YUN；类: ZhanPoMingYun；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
@@ -810,7 +799,7 @@
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>斩破命运</t>
+          <t>迷惑一击</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -828,7 +817,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>造成7/9点伤害。；预见2/3。；抽1张牌。</t>
+          <t>造成8点伤害。；{IfUpgraded:show:选择1张牌触发灵感。|随机1张牌触发灵感。}</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -838,7 +827,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-ZHAN_PO_MING_YUN；类: ZhanPoMingYun；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-MI_HUO_YI_JI；类: MiHuoYiJi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
@@ -846,7 +835,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>迷惑一击</t>
+          <t>雪</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -864,7 +853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>造成8点伤害。；{IfUpgraded:show:选择1张牌触发灵感。|随机1张牌触发灵感。}</t>
+          <t>造成6/9点伤害。；获得1层雪。；灵感：抽1张牌。</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -874,7 +863,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-MI_HUO_YI_JI；类: MiHuoYiJi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-XUE；类: Xue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H11" s="2" t="n"/>
@@ -882,7 +871,7 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>雪</t>
+          <t>一现</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -895,12 +884,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。；获得1层雪。；灵感：抽1张牌。</t>
+          <t>抽2/3张牌。；灵感：抽1张牌。</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -910,7 +899,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-XUE；类: Xue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YI_XIAN；类: YiXian；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -918,11 +907,11 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>高速斩击</t>
+          <t>天眼</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -931,12 +920,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成12点伤害。；抽2/3张牌。；灵感：这张牌费用减少1。</t>
+          <t>获得7/9点格挡。；预见3/5。</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -946,7 +935,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-GAO_SU_ZHAN_JI；类: GaoSuZhanJi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TIAN_YAN；类: TianYan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H13" s="2" t="n"/>
@@ -954,7 +943,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>一现</t>
+          <t>月光</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -972,17 +961,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>抽2/3张牌。；灵感：抽1张牌。</t>
+          <t>凝聚1。</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YI_XIAN；类: YiXian；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YUE_GUANG；类: YueGuang；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H14" s="2" t="n"/>
@@ -990,7 +979,7 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>天眼</t>
+          <t>花</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1003,22 +992,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>获得7/9点格挡。；预见3/5。</t>
+          <t>造成6/9点伤害。；获得1层花。；黑云：额外攻击1次。</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_YAN；类: TianYan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HUA；类: Hua；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H15" s="2" t="n"/>
@@ -1026,7 +1015,7 @@
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>寒冰庇护</t>
+          <t>黑云奥义：影</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1039,22 +1028,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>获得7/10点格挡。；抽1张牌。；灵感：再抽1张牌。</t>
+          <t>造成3/5点伤害2次。；黑云：额外攻击2次；否则，获得2层无明。</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HAN_BING_BI_HU；类: HanBingBiHu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YING_FU；类: HeiYunMiFaYingFu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H16" s="2" t="n"/>
@@ -1062,7 +1051,7 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>咒术</t>
+          <t>黑云奥义：灭</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1075,22 +1064,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>升级你手中的月影。；凝聚1。</t>
+          <t>造成9/12点伤害。；黑云：额外攻击1次；否则，施加1层虚弱。</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-ZHOU_SHU；类: ZhouShu；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_MIE；类: HeiYunAoYiMie；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H17" s="2" t="n"/>
@@ -1098,7 +1087,7 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>圆舞</t>
+          <t>黑云秘法：积雨</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1116,17 +1105,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>获得8点格挡。；你手中的月影伤害+3/5。</t>
+          <t>获得8/11点格挡。；在你的下回合开始时，进入黑云姿态。</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YUAN_WU；类: YuanWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JI_YU；类: HeiYunMiFaJiYu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H18" s="2" t="n"/>
@@ -1134,7 +1123,7 @@
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>月光</t>
+          <t>刀鞘打击</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1147,22 +1136,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>凝聚1。；你手中的月影伤害+5/8。</t>
+          <t>造成8/11点伤害。；在下个回合获得1。</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YUE_GUANG；类: YueGuang；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-DAO_QIAO_DA_JI；类: DaoQiaoDaJi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H19" s="2" t="n"/>
@@ -1170,7 +1159,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>斩钢闪</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1188,17 +1177,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。；获得1层花。；黑云：额外攻击1次。</t>
+          <t>造成9/12点伤害。；连续3回合打出斩钢闪，将一张居合加入手牌。</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUA；类: Hua；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-ZHAN_GANG_SHAN；类: ZhanGangShan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
@@ -1206,7 +1195,7 @@
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：影</t>
+          <t>月</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1224,17 +1213,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>造成3/5点伤害2次。；黑云：额外攻击2次；否则，获得2层黑云。</t>
+          <t>造成6/9点伤害。；获得1层月。；你手中的月影伤害+3。</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YING_FU；类: HeiYunMiFaYingFu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YUE；类: Yue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H21" s="2" t="n"/>
@@ -1242,11 +1231,11 @@
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：殇</t>
+          <t>一击必杀！居合抽卡</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -1255,22 +1244,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；黑云：施加2层易伤；否则，获得2层黑云。</t>
+          <t>选择1张手牌弃掉。；抽1张牌。；如果抽到的是一击必杀！居合抽卡，将{IfUpgraded:show:1张居合+|1张居合}加入手中。</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_SHANG；类: HeiYunAoYiShang；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YI_JI_BI_SHA_JU_HE_CHOU_KA；类: YiJiBiShaJuHeChouKa；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H22" s="2" t="n"/>
@@ -1278,7 +1267,7 @@
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：灭</t>
+          <t>人剑合一</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -1291,22 +1280,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；黑云：额外攻击1次；否则，施加1层虚弱。</t>
+          <t>获得8/11点格挡。；在接下来的2个回合开始时，各额外抽1张牌。</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_MIE；类: HeiYunAoYiMie；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-REN_JIAN_HE_YI；类: RenJianHeYi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H23" s="2" t="n"/>
@@ -1314,7 +1303,7 @@
     <row r="24" ht="48" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>拨日见云</t>
+          <t>回念</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1332,17 +1321,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>预见3/5。；在你的下回合开始时，进入黑云姿态并抽1张牌。</t>
+          <t>获得7/10点格挡。；将你弃牌堆中的1张牌放到抽牌堆顶部。</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BO_RI_JIAN_YUN；类: BoRiJianYun；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HUI_NIAN；类: HuiNian；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H24" s="2" t="n"/>
@@ -1350,11 +1339,11 @@
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：残</t>
+          <t>未雨绸缪</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1368,17 +1357,17 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>抽1张牌。；进入黑云姿态。</t>
+          <t>获得5/8点格挡。；抽2张牌。；将1张手牌置于抽牌堆顶部。</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_CAN；类: HeiYunAoYiCan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-WEI_YU_CHOU_MOU；类: WeiYuChouMou；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H25" s="2" t="n"/>
@@ -1386,7 +1375,7 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：积雨</t>
+          <t>严寒</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -1394,27 +1383,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>获得8/11点格挡。；在你的下回合开始时，进入黑云姿态。</t>
+          <t>造成5/8点伤害。；抽1张牌。；灵感：额外释放1次。</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JI_YU；类: HeiYunMiFaJiYu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YAN_HAN；类: YanHan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H26" s="2" t="n"/>
@@ -1422,7 +1411,7 @@
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：隼武</t>
+          <t>冰雪</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1430,27 +1419,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>获得5/8点格挡。；黑云：获得5/8点格挡；否则，下次进入黑云姿态时抽2张牌。</t>
+          <t>造成4点伤害2/3次。；抽1张牌，优先抽灵感牌。</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_SUN_WU；类: HeiYunMiFaSunWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BING_XUE；类: BingXue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H27" s="2" t="n"/>
@@ -1458,7 +1447,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：魂佑</t>
+          <t>破冰斩</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1466,27 +1455,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>获得5/8点格挡。；黑云：获得5/8点格挡；否则，下次进入黑云姿态时获得1。</t>
+          <t>选择1张手牌消耗。；对所有敌人造成7/10点伤害。；灵感：额外攻击一次。</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_HUN_YOU；类: HeiYunMiFaHunYou；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-PO_BING_ZHAN；类: PoBingZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H28" s="2" t="n"/>
@@ -1494,15 +1483,15 @@
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>刀鞘打击</t>
+          <t>高速斩击</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1512,17 +1501,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>造成8/11点伤害。；在下个回合获得1。</t>
+          <t>对所有敌人造成12点伤害。；抽2/3张牌。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-DAO_QIAO_DA_JI；类: DaoQiaoDaJi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-GAO_SU_ZHAN_JI；类: GaoSuZhanJi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H29" s="2" t="n"/>
@@ -1530,7 +1519,7 @@
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>妖怪狩猎</t>
+          <t>命定</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -1538,27 +1527,27 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>造成2点伤害2/3次。；凝聚1。</t>
+          <t>预见3/5。；抽2张牌。</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YAO_GUAI_SHOU_LIE；类: YaoGuaiShouLie；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-MING_DING；类: MingDing；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H30" s="2" t="n"/>
@@ -1566,35 +1555,35 @@
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>彼岸花</t>
+          <t>天际</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。\n在接下来的2个回合开始时，造成6/9点伤害。</t>
+          <t>把你的手牌放到抽牌堆顶部。；抽等量的牌。；灵感：抽1张牌。</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BI_AN_HUA；类: BiAnHua；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TIAN_JI；类: TianJi；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H31" s="2" t="n"/>
@@ -1602,35 +1591,35 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>斩钢闪</t>
+          <t>寒冰庇护</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；连续3回合打出斩钢闪，将一张居合加入手牌。</t>
+          <t>获得12/16点格挡。；在你的下回合开始时，抽2张牌。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-ZHAN_GANG_SHAN；类: ZhanGangShan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HAN_BING_BI_HU；类: HanBingBiHu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H32" s="2" t="n"/>
@@ -1638,35 +1627,35 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>明镜止水</t>
+          <t>灵光</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。；你的下一张攻击牌费用减少1。</t>
+          <t>抽2/3张牌。</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YI_SHI；类: YiShi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-LING_GUANG；类: LingGuang；牌池: 主牌池；源码关键词: Exhaust</t>
         </is>
       </c>
       <c r="H33" s="2" t="n"/>
@@ -1674,7 +1663,7 @@
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>先见之明</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1682,27 +1671,27 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。；获得1层月。；你手中的月影伤害+3。</t>
+          <t>回合开始时，预见3/4。</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YUE；类: Yue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-XIAN_JIAN_ZHI_MING；类: XianJianZhiMing；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H34" s="2" t="n"/>
@@ -1710,35 +1699,35 @@
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>轮回斩</t>
+          <t>冰点之刃</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害3/4次。\n每次抽到时，费用在本场战斗中减少1。</t>
+          <t>当灵感触发时，对随机敌人造成4/6点伤害。</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LUN_HUI_ZHAN；类: LunHuiZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BING_DIAN_ZHI_REN；类: BingDianZhiRen；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H35" s="2" t="n"/>
@@ -1746,15 +1735,15 @@
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>一击必杀！居合抽卡</t>
+          <t>咒术</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1764,17 +1753,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>选择1张手牌弃掉。；抽1张牌。；如果抽到的是一击必杀！居合抽卡，将{IfUpgraded:show:1张居合+|1张居合}加入手中。</t>
+          <t>升级你手中的月影。；你手中的月影伤害+5。</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YI_JI_BI_SHA_JU_HE_CHOU_KA；类: YiJiBiShaJuHeChouKa；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-ZHOU_SHU；类: ZhouShu；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H36" s="2" t="n"/>
@@ -1782,15 +1771,15 @@
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>人剑合一</t>
+          <t>圆舞</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1800,17 +1789,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>获得8/11点格挡。；在接下来的2个回合开始时，各额外抽1张牌。</t>
+          <t>获得11/15点格挡。；凝聚1。</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-REN_JIAN_HE_YI；类: RenJianHeYi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YUAN_WU；类: YuanWu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H37" s="2" t="n"/>
@@ -1818,15 +1807,15 @@
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>人格切换</t>
+          <t>拨云见日</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1836,17 +1825,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>将2/1张手牌放回抽牌堆顶部。；抽2张牌。</t>
+          <t>获得3/4层无明。；在你的下回合开始时，进入黑云姿态。</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-REN_GE_QIE_HUAN；类: RenGeQieHuan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BO_RI_JIAN_YUN；类: BoRiJianYun；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
@@ -1854,7 +1843,7 @@
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>剑心</t>
+          <t>黑云奥义：残</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -1862,7 +1851,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1872,17 +1861,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>抽1张牌。</t>
+          <t>抽1张牌。；进入黑云姿态。</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-JIAN_XIN；类: JianXin；牌池: 主牌池；源码关键词: Retain</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_CAN；类: HeiYunAoYiCan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H39" s="2" t="n"/>
@@ -1890,7 +1879,7 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>回念</t>
+          <t>黑云秘法：降临</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1898,7 +1887,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1908,17 +1897,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>获得7/10点格挡。；将你弃牌堆中的1张牌放到抽牌堆顶部。</t>
+          <t>获得9/12点格挡。；下次进入黑云姿态时，对所有敌人施加1层易伤。</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUI_NIAN；类: HuiNian；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JIANG_LIN；类: HeiYunMiFaJiangLin；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H40" s="2" t="n"/>
@@ -1926,15 +1915,15 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>招架</t>
+          <t>黑云秘法：魂佑</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1944,17 +1933,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>获得5/8点格挡。；本回合每打出一张牌，使获得的格挡+1。；如果刚好抵挡全部伤害，下回合开始时获得一张居合。</t>
+          <t>获得12点格挡。；黑云：获得12点格挡；否则，下次进入黑云姿态时获得1/2。</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-ZHAO_JIA；类: ZhaoJia；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_HUN_YOU；类: HeiYunMiFaHunYou；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H41" s="2" t="n"/>
@@ -1962,7 +1951,7 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>未雨绸缪</t>
+          <t>黑雾降临</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1970,27 +1959,27 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>通常</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>获得5/8点格挡。；抽2张牌。；将1张手牌置于抽牌堆顶部。</t>
+          <t>回合开始时，进入黑云姿态。</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-WEI_YU_CHOU_MOU；类: WeiYuChouMou；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_WU_JIANG_LIN；类: HeiWuJiangLin；牌池: 主牌池；源码关键词: Innate</t>
         </is>
       </c>
       <c r="H42" s="2" t="n"/>
@@ -1998,7 +1987,7 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>冰雪</t>
+          <t>剑舞</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -2016,17 +2005,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>造成4点伤害2/3次。；抽1张牌，优先抽灵感牌。</t>
+          <t>根据本回合额外抽牌的数量造成5/7点伤害（当前{CurrentHitCount}次）。</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BING_XUE；类: BingXue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-JIAN_WU；类: JianWu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H43" s="2" t="n"/>
@@ -2034,7 +2023,7 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>破冰斩</t>
+          <t>妖怪狩猎</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -2052,17 +2041,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>选择1张手牌消耗。；对所有敌人造成7/10点伤害。；灵感：额外攻击一次。</t>
+          <t>造成2点伤害2/3次。；凝聚1。</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-PO_BING_ZHAN；类: PoBingZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YAO_GUAI_SHOU_LIE；类: YaoGuaiShouLie；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H44" s="2" t="n"/>
@@ -2070,7 +2059,7 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>命定</t>
+          <t>幻变斩</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -2083,22 +2072,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>预见3/5。；抽2张牌。</t>
+          <t>造成3点伤害2/3次。；消耗1张手牌。；抽1张牌。</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-MING_DING；类: MingDing；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HUAN_BIAN_ZHAN；类: HuanBianZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H45" s="2" t="n"/>
@@ -2106,7 +2095,7 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>天际</t>
+          <t>影月</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -2119,22 +2108,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>把你的手牌放到抽牌堆顶部。；抽等量的牌。；灵感：抽1张牌。</t>
+          <t>造成5点伤害。；这张牌视为月影。；{IfUpgraded:show:每当你使用其他攻击命中时，这张牌伤害+1。|}</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_JI；类: TianJi；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-SHADOW_MOON；类: ShadowMoon；牌池: 主牌池；源码关键词: Retain, Exhaust</t>
         </is>
       </c>
       <c r="H46" s="2" t="n"/>
@@ -2142,11 +2131,11 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>灵光</t>
+          <t>彼岸花</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
@@ -2155,22 +2144,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>抽2/3张牌。</t>
+          <t>造成6/9点伤害。\n在接下来的2个回合开始时，造成6/9点伤害。</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LING_GUANG；类: LingGuang；牌池: 主牌池；源码关键词: Exhaust</t>
+          <t>ID: YUKIMOD-BI_AN_HUA；类: BiAnHua；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H47" s="2" t="n"/>
@@ -2178,7 +2167,7 @@
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>先见之明</t>
+          <t>明镜止水</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2191,22 +2180,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，预见3/4。</t>
+          <t>造成6/9点伤害。；你的下一张攻击牌费用减少1。</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-XIAN_JIAN_ZHI_MING；类: XianJianZhiMing；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YI_SHI；类: YiShi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H48" s="2" t="n"/>
@@ -2214,11 +2203,11 @@
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>冰点之刃</t>
+          <t>踏前斩</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -2227,22 +2216,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>当灵感触发时，对随机敌人造成4/6点伤害。</t>
+          <t>造成2/4点伤害。；对这回合没被踏前斩命中的敌人释放时返回手牌。</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BING_DIAN_ZHI_REN；类: BingDianZhiRen；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TA_QIAN_ZHAN；类: TaQianZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H49" s="2" t="n"/>
@@ -2250,11 +2239,11 @@
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：虚像</t>
+          <t>轮回斩</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
@@ -2263,22 +2252,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>施加2/3层虚弱。；获得2/3层黑云。；在你的下回合开始时，进入黑云姿态。</t>
+          <t>造成5点伤害3/4次。\n每次抽到时，费用在本场战斗中减少1。</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_XU_XIANG；类: HeiYunMiFaXuXiang；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-LUN_HUI_ZHAN；类: LunHuiZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H50" s="2" t="n"/>
@@ -2286,11 +2275,11 @@
     <row r="51" ht="48" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：降临</t>
+          <t>人格切换</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
@@ -2304,17 +2293,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>获得8/11点格挡。；下次进入黑云姿态时，对所有敌人施加1层易伤。</t>
+          <t>将2/1张手牌放回抽牌堆顶部。；抽2张牌。</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JIANG_LIN；类: HeiYunMiFaJiangLin；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-REN_GE_QIE_HUAN；类: RenGeQieHuan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H51" s="2" t="n"/>
@@ -2322,11 +2311,11 @@
     <row r="52" ht="48" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>如影随形</t>
+          <t>剑心</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
@@ -2335,22 +2324,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，若你处于黑云姿态，则抽1张牌，优先黑云牌。</t>
+          <t>至多消耗1/2张手牌。抽等量的牌。</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-RU_YING_SUI_XING；类: RuYingSuiXing；牌池: 主牌池；源码关键词: Innate</t>
+          <t>ID: YUKIMOD-JIAN_XIN；类: JianXin；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H52" s="2" t="n"/>
@@ -2358,7 +2347,7 @@
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>引雷天云</t>
+          <t>招架</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -2371,22 +2360,22 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>处于黑云姿态时，获得3/4点力量。</t>
+          <t>获得{Block:diff()}点格挡。；本回合每打出一张牌，使获得的格挡+1。；如果刚好抵挡全部伤害，下回合开始时获得一张居合。</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YIN_LEI_TIAN_YUN；类: YinLeiTianYun；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-ZHAO_JIA；类: ZhaoJia；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H53" s="2" t="n"/>
@@ -2394,7 +2383,7 @@
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>黑雾降临</t>
+          <t>映月</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -2407,22 +2396,22 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，进入黑云姿态。</t>
+          <t>下次打出月影时，将1张相同的复制加入手中。</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_WU_JIANG_LIN；类: HeiWuJiangLin；牌池: 主牌池；源码关键词: Innate</t>
+          <t>ID: YUKIMOD-YING_YUE_MIRROR；类: YingYueMirror；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H54" s="2" t="n"/>
@@ -2430,11 +2419,11 @@
     <row r="55" ht="48" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>剑舞</t>
+          <t>背水</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
@@ -2443,12 +2432,12 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>根据本回合额外抽牌的数量造成5/7点伤害（当前{CurrentHitCount}次）。</t>
+          <t>获得2/3。；你在本回合内不能再抽任何牌。</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2458,7 +2447,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-JIAN_WU；类: JianWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BEI_SHUI；类: BeiShui；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H55" s="2" t="n"/>
@@ -2466,11 +2455,11 @@
     <row r="56" ht="48" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>幻变斩</t>
+          <t>起手式</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
@@ -2479,12 +2468,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>造成3点伤害2/3次。；消耗1张手牌。；抽1张牌。</t>
+          <t>获得1。</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2494,7 +2483,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUAN_BIAN_ZHAN；类: HuanBianZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-QI_SHOU_SHI；类: QiShouShi；牌池: 主牌池；源码关键词: Retain, Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H56" s="2" t="n"/>
@@ -2502,7 +2491,7 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>看破</t>
+          <t>怒涛斩</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
@@ -2515,12 +2504,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。；将抽牌堆中的1张牌放入你的手牌。</t>
+          <t>一回合内首次打出3张攻击牌时，获得1。</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2530,7 +2519,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-KAN_PO；类: KanPo；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-NU_TAO_ZHAN；类: NuTaoZhan；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H57" s="2" t="n"/>
@@ -2538,11 +2527,11 @@
     <row r="58" ht="48" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>踏前斩</t>
+          <t>满月</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
@@ -2551,12 +2540,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>造成2/4点伤害。；对这回合没被踏前斩命中的敌人释放时返回手牌。</t>
+          <t>每当你使用1张牌，你手中的月影伤害+2/3。</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2566,7 +2555,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TA_QIAN_ZHAN；类: TaQianZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-MAN_YUE；类: ManYue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H58" s="2" t="n"/>
@@ -2574,11 +2563,11 @@
     <row r="59" ht="48" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>零式</t>
+          <t>盈月</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -2587,12 +2576,12 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>造成4/5点伤害。；将1张{IfUpgraded:show:一式+|一式}加入手中。</t>
+          <t>回合结束时，你手中的月影伤害增加5/7。</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2602,7 +2591,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LING_SHI；类: LingShi；牌池: 主牌池；源码关键词: Exhaust</t>
+          <t>ID: YUKIMOD-YING_YUE；类: YingYue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H59" s="2" t="n"/>
@@ -2610,7 +2599,7 @@
     <row r="60" ht="48" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>映月</t>
+          <t>蓝月</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -2623,12 +2612,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>下次打出月影时，将1张相同的复制加入手中。</t>
+          <t>当灵感触发时，你手中的月影伤害+3/5。</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2638,7 +2627,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YING_YUE_MIRROR；类: YingYueMirror；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-LAN_YUE；类: LanYue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H60" s="2" t="n"/>
@@ -2646,7 +2635,7 @@
     <row r="61" ht="48" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>暗月</t>
+          <t>血月</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -2659,12 +2648,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>你手中的月影获得：；黑云：伤害增加50%。</t>
+          <t>当你在黑云姿态下使用牌时，你手中的月影伤害+3/5。</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2674,7 +2663,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-AN_YUE；类: AnYue；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-XUE_YUE；类: XueYue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H61" s="2" t="n"/>
@@ -2682,15 +2671,15 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>红尘</t>
+          <t>拔刀斩</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2700,17 +2689,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>获得1。；抽2/3张牌。；你在本回合内不能再抽任何牌。</t>
+          <t>抽1张牌并打出。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HONG_CHEN；类: HongChen；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BA_DAO_ZHAN；类: BaDaoZhan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H62" s="2" t="n"/>
@@ -2718,15 +2707,15 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>背水</t>
+          <t>雪影</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2736,17 +2725,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>获得2/3。；你在本回合内不能再抽任何牌。</t>
+          <t>抽2张牌。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BEI_SHUI；类: BeiShui；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-XUE_YING；类: XueYing；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H63" s="2" t="n"/>
@@ -2754,35 +2743,35 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>起手式</t>
+          <t>寒霜</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>获得1。</t>
+          <t>回合开始时，随机触发1/2张手中的灵感。</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-QI_SHOU_SHI；类: QiShouShi；牌池: 主牌池；源码关键词: Retain, Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-HAN_SHUANG；类: HanShuang；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H64" s="2" t="n"/>
@@ -2790,7 +2779,7 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>怒涛斩</t>
+          <t>沉思</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -2798,7 +2787,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2808,17 +2797,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>一回合内打出3张攻击牌时，抽1张牌。</t>
+          <t>当灵感触发时，获得2/3点格挡。</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-NU_TAO_ZHAN；类: NuTaoZhan；牌池: 主牌池；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-CHEN_SI；类: ChenSi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H65" s="2" t="n"/>
@@ -2826,7 +2815,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>朔月</t>
+          <t>零度</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2834,7 +2823,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2844,17 +2833,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，如果你的手中没有真正的月影，则凝聚1。</t>
+          <t>当你触发12/9次灵感时，将1张居合加入手中。</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHUO_YUE；类: ShuoYue；牌池: 主牌池；源码关键词: Innate</t>
+          <t>ID: YUKIMOD-LING_DU；类: LingDu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H66" s="2" t="n"/>
@@ -2862,7 +2851,7 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>满月</t>
+          <t>黑云奥义：黑雾</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -2870,27 +2859,27 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>每当你使用1张牌，你手中的月影伤害+2/3。</t>
+          <t>造成8/10点伤害。；黑云：你手中每有1张技能牌，额外攻击1次；否则，获得3层无明。</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-MAN_YUE；类: ManYue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_HEI_WU；类: HeiYunAoYiHeiWu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H67" s="2" t="n"/>
@@ -2898,35 +2887,35 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>盈月</t>
+          <t>黑云心法</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>回合结束时，你手中的月影伤害增加5/7。</t>
+          <t>本回合内保留黑云姿态。</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YING_YUE；类: YingYue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_XIN_FA；类: HeiYunXinFa；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H68" s="2" t="n"/>
@@ -2934,7 +2923,7 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>蓝月</t>
+          <t>黑云秘法：出鞘</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
@@ -2942,27 +2931,27 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>当灵感触发时，你手中的月影伤害+3/5。</t>
+          <t>进入黑云姿态。；下次退出黑云姿态时，将1张{IfUpgraded:show:纳刀+|纳刀}加入手中。</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LAN_YUE；类: LanYue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_CHU_QIAO；类: HeiYunMiFaChuQiao；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H69" s="2" t="n"/>
@@ -2970,7 +2959,7 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>血月</t>
+          <t>黑云秘法：幕临</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
@@ -2978,27 +2967,27 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>当你在黑云姿态下使用牌时，你手中的月影伤害+3/5。</t>
+          <t>黑云：获得1，抽1张牌，保留黑云姿态；否则，下次进入黑云姿态时额外获得2点能量，抽2张牌。</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-XUE_YUE；类: XueYue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_MU_LIN；类: HeiYunMiFaMuLin；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H70" s="2" t="n"/>
@@ -3006,11 +2995,11 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>拔刀斩</t>
+          <t>黑云秘法：燕回</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
@@ -3024,17 +3013,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>抽1张牌并打出。；灵感：这张牌费用减少1。</t>
+          <t>将抽牌堆或弃牌堆中的随机1张黑云牌加入手中。；黑云：保留黑云姿态。</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BA_DAO_ZHAN；类: BaDaoZhan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YAN_HUI；类: HeiYunMiFaYanHui；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H71" s="2" t="n"/>
@@ -3042,7 +3031,7 @@
     <row r="72" ht="48" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>雪影</t>
+          <t>黑云秘法：霞阵</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
@@ -3055,22 +3044,22 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>抽2张牌。；灵感：这张牌费用减少1。</t>
+          <t>回合开始时，获得2/3层无明。</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-XUE_YING；类: XueYing；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_XIA_ZHEN；类: HeiYunMiFaXiaZhen；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H72" s="2" t="n"/>
@@ -3078,7 +3067,7 @@
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：回转</t>
+          <t>业火</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
@@ -3091,22 +3080,22 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>抽1张黑云牌。；灵感：获得2/3层黑云。；黑云：抽2张牌；否则，进入黑云姿态。</t>
+          <t>造成5点伤害。；每当你攻击该目标时，手中月影伤害+2/3。</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_JI_HUI_ZHUAN；类: HeiYunMiJiHuiZhuan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YE_HUO；类: YeHuo；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H73" s="2" t="n"/>
@@ -3114,7 +3103,7 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>寒霜</t>
+          <t>燕回反</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
@@ -3127,22 +3116,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，随机触发1/2张手中的灵感。</t>
+          <t>释放你上一个释放的攻击1次。</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HAN_SHUANG；类: HanShuang；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YAN_HUI_FAN；类: YanHuiFan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H74" s="2" t="n"/>
@@ -3150,7 +3139,7 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>沉思</t>
+          <t>看破</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
@@ -3163,22 +3152,22 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>当灵感触发时，获得2/3点格挡。</t>
+          <t>造成9/12点伤害。；将抽牌堆中的1张牌放入你的手牌。</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-CHEN_SI；类: ChenSi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-KAN_PO；类: KanPo；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H75" s="2" t="n"/>
@@ -3186,7 +3175,7 @@
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>零度</t>
+          <t>荣誉</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
@@ -3199,22 +3188,22 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>当你触发12/9次灵感时，将1张居合加入手中。</t>
+          <t>造成9/12点伤害。；如果击杀目标，则将一张居合加入手中。</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LING_DU；类: LingDu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-RONG_YU；类: RongYu；牌池: 主牌池；源码关键词: Exhaust</t>
         </is>
       </c>
       <c r="H76" s="2" t="n"/>
@@ -3222,11 +3211,11 @@
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>霜降</t>
+          <t>零式</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
@@ -3235,22 +3224,22 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>你的打击牌也可以触发灵感。；其灵感效果：费用减少1。</t>
+          <t>造成4/5点伤害。；将1张{IfUpgraded:show:一式+|一式}加入手中。</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHUANG_JIANG；类: ShuangJiang；牌池: 主牌池；源码关键词: Innate</t>
+          <t>ID: YUKIMOD-LING_SHI；类: LingShi；牌池: 主牌池；源码关键词: Exhaust</t>
         </is>
       </c>
       <c r="H77" s="2" t="n"/>
@@ -3258,7 +3247,7 @@
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：黑雾</t>
+          <t>回天</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
@@ -3271,22 +3260,22 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>造成7/9点伤害。；黑云：你手中每有1张技能牌，额外攻击1次；否则，你手中每有1张攻击牌，额外攻击1次。</t>
+          <t>下一张攻击牌额外释放1次。</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_HEI_WU；类: HeiYunAoYiHeiWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HUI_TIAN；类: HuiTian；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H78" s="2" t="n"/>
@@ -3294,11 +3283,11 @@
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>黑云心法</t>
+          <t>月读</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
@@ -3312,17 +3301,17 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>本回合内保留黑云姿态。；黑云：本回合内获得2/3点力量。</t>
+          <t>本回合内，你的攻击命中时，手中月影伤害+2/3。</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_XIN_FA；类: HeiYunXinFa；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YUE_DU；类: YueDu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H79" s="2" t="n"/>
@@ -3330,7 +3319,7 @@
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：出鞘</t>
+          <t>残月</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
@@ -3348,17 +3337,17 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>进入黑云姿态。；下次退出黑云姿态时，将1张{IfUpgraded:show:纳刀+|纳刀}加入手中。</t>
+          <t>凝聚1。；你手中的月影费用减少1。</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_CHU_QIAO；类: HeiYunMiFaChuQiao；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-CAN_YUE；类: CanYue；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H80" s="2" t="n"/>
@@ -3366,11 +3355,11 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：幕临</t>
+          <t>红尘</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -3384,17 +3373,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>黑云：获得1，抽1张牌，保留黑云姿态；否则，下次进入黑云姿态时额外获得2点能量，抽2张牌。</t>
+          <t>获得1。；抽2/3张牌。；你在本回合内不能再抽任何牌。</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_MU_LIN；类: HeiYunMiFaMuLin；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-HONG_CHEN；类: HongChen；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H81" s="2" t="n"/>
@@ -3402,11 +3391,11 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：燕回</t>
+          <t>天刀形态</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
@@ -3415,22 +3404,22 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>将抽牌堆或弃牌堆中的随机1张黑云牌加入手中。；黑云：保留黑云姿态。</t>
+          <t>每回合打出的第一张攻击牌额外打出一次。</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YAN_HUI；类: HeiYunMiFaYanHui；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-TIAN_DAO_XING_TAI；类: TianDaoXingTai；牌池: 主牌池；源码关键词: Retain</t>
         </is>
       </c>
       <c r="H82" s="2" t="n"/>
@@ -3438,7 +3427,7 @@
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：霞阵</t>
+          <t>振刀</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
@@ -3456,17 +3445,17 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，获得2/3层黑云。</t>
+          <t>每花费3/2费，抽1张牌。</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_XIA_ZHEN；类: HeiYunMiFaXiaZhen；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-ZHEN_DAO；类: ZhenDao；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H83" s="2" t="n"/>
@@ -3474,7 +3463,7 @@
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>业火</t>
+          <t>朔月</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
@@ -3487,12 +3476,12 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害。；每当你攻击该目标时，手中月影伤害+2/3。</t>
+          <t>回合结束时，凝聚1。</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3502,19 +3491,19 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YE_HUO；类: YeHuo；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-SHUO_YUE；类: ShuoYue；牌池: 主牌池；源码关键词: Innate</t>
         </is>
       </c>
       <c r="H84" s="2" t="n"/>
     </row>
-    <row r="85" ht="47.6" customHeight="1">
+    <row r="85" ht="48" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>影月</t>
+          <t>满溢</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
@@ -3523,12 +3512,12 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害。；这张牌视为月影。；{IfUpgraded:show:每当你使用其他攻击命中时，这张牌伤害+1（当前{CurrentDamage}）。|}</t>
+          <t>每回合第一次抽满手牌时，获得2费。</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -3538,7 +3527,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHADOW_MOON；类: ShadowMoon；牌池: 主牌池；源码关键词: Retain, Exhaust</t>
+          <t>ID: YUKIMOD-MAN_YI；类: ManYi；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H85" s="2" t="n"/>
@@ -3546,7 +3535,7 @@
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>燕回反</t>
+          <t>瞬念</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -3559,12 +3548,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>释放你上一个释放的攻击2次。</t>
+          <t>回合开始时，将1张随机的{IfUpgraded:show:升级过的}灵感牌加入手中。</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3574,7 +3563,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YAN_HUI_FAN；类: YanHuiFan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-SHUN_NIAN；类: ShunNian；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H86" s="2" t="n"/>
@@ -3582,7 +3571,7 @@
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>荣誉</t>
+          <t>黄昏的羁绊</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
@@ -3595,12 +3584,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；如果击杀目标，则将一张居合加入手中。</t>
+          <t>你不能额外获得费用。；回合开始时，随机2张手牌下次使用前费用减少1。</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -3610,7 +3599,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-RONG_YU；类: RongYu；牌池: 主牌池；源码关键词: Exhaust</t>
+          <t>ID: YUKIMOD-HUANG_HUN_DE_JI_BAN；类: HuangHunDeJiBan；牌池: 主牌池；源码关键词: Innate；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H87" s="2" t="n"/>
@@ -3618,15 +3607,15 @@
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>回天</t>
+          <t>神丶压制准备</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>先古</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3636,17 +3625,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>下一张攻击牌额外释放1次。</t>
+          <t>从抽牌堆或弃牌堆抽尽可能多的攻击牌。；获得2/5层活力。；灵感：优先抽灵感牌。</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUI_TIAN；类: HuiTian；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-SHEN_YA_ZHI_ZHUN_BEI；类: ShenYaZhiZhunBei；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H88" s="2" t="n"/>
@@ -3654,25 +3643,25 @@
     <row r="89" ht="48" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>月读</t>
+          <t>天际斩击</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>先古</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>本回合内，你的攻击命中时，手中月影伤害+2/3。</t>
+          <t>回合开始时，将手中所有牌放到抽牌堆顶部，并抽出那个数量+2的牌。</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -3682,7 +3671,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YUE_DU；类: YueDu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TIAN_JI_ZHAN_JI；类: TianJiZhanJi；牌池: 主牌池；源码关键词: Innate</t>
         </is>
       </c>
       <c r="H89" s="2" t="n"/>
@@ -3690,7 +3679,7 @@
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>残月</t>
+          <t>黑云奥义：殇</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -3698,27 +3687,27 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>凝聚1。；你手中的月影费用减少1。</t>
+          <t>造成9/12点伤害。；黑云：施加2层易伤；否则，获得2层无明。</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-CAN_YUE；类: CanYue；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_SHANG；类: HeiYunAoYiShang；牌池: 无卡池</t>
         </is>
       </c>
       <c r="H90" s="2" t="n"/>
@@ -3726,7 +3715,7 @@
     <row r="91" ht="48" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>上弦之月</t>
+          <t>黑云秘法：隼武</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
@@ -3734,27 +3723,27 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>当你打出的月影单次命中伤害达到50或更高时，将1张居合加入手中。</t>
+          <t>获得5/8点格挡。；黑云：获得5/8点格挡；否则，下次进入黑云姿态时抽2张牌。</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHANG_XIAN_ZHI_YUE；类: ShangXianZhiYue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_SUN_WU；类: HeiYunMiFaSunWu；牌池: 无卡池</t>
         </is>
       </c>
       <c r="H91" s="2" t="n"/>
@@ -3762,35 +3751,35 @@
     <row r="92" ht="48" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>天刀形态</t>
+          <t>黑云秘法：回转</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>每回合打出的第一张攻击牌额外打出一次。</t>
+          <t>抽1张黑云牌。；灵感：获得2/3层无明。；黑云：抽2张牌；否则，进入黑云姿态。</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_DAO_XING_TAI；类: TianDaoXingTai；牌池: 主牌池；源码关键词: Retain</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_JI_HUI_ZHUAN；类: HeiYunMiJiHuiZhuan；牌池: 无卡池</t>
         </is>
       </c>
       <c r="H92" s="2" t="n"/>
@@ -3798,7 +3787,7 @@
     <row r="93" ht="48" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>振刀</t>
+          <t>黑云秘法：虚像</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -3806,27 +3795,27 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>每花费4/3费，抽1张牌。</t>
+          <t>施加2/3层虚弱。；获得2/3层无明。</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-ZHEN_DAO；类: ZhenDao；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_XU_XIANG；类: HeiYunMiFaXuXiang；牌池: 无卡池</t>
         </is>
       </c>
       <c r="H93" s="2" t="n"/>
@@ -3834,7 +3823,7 @@
     <row r="94" ht="48" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>满溢</t>
+          <t>如影随形</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
@@ -3842,7 +3831,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3852,17 +3841,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>每回合第一次抽满手牌时，获得2费。</t>
+          <t>回合开始时，若你处于黑云姿态，则抽1张牌，优先黑云牌。</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-MAN_YI；类: ManYi；牌池: 主牌池；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-RU_YING_SUI_XING；类: RuYingSuiXing；牌池: 无卡池；源码关键词: Innate</t>
         </is>
       </c>
       <c r="H94" s="2" t="n"/>
@@ -3870,7 +3859,7 @@
     <row r="95" ht="48" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>瞬念</t>
+          <t>引雷天云</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -3878,7 +3867,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3888,17 +3877,17 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，将1张随机的{IfUpgraded:show:升级过的}灵感牌加入手中。</t>
+          <t>进入黑云姿态时，获得5/8层活力。</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHUN_NIAN；类: ShunNian；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YIN_LEI_TIAN_YUN；类: YinLeiTianYun；牌池: 无卡池</t>
         </is>
       </c>
       <c r="H95" s="2" t="n"/>
@@ -3906,7 +3895,7 @@
     <row r="96" ht="48" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>黄昏的羁绊</t>
+          <t>暗月</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
@@ -3914,17 +3903,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>你不能额外获得费用。；回合开始时，随机2张手牌下次使用前费用减少1。</t>
+          <t>你手中的月影获得：；黑云：伤害增加50%。</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -3934,7 +3923,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUANG_HUN_DE_JI_BAN；类: HuangHunDeJiBan；牌池: 主牌池；源码关键词: Innate；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-AN_YUE；类: AnYue；牌池: 无卡池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H96" s="2" t="n"/>
@@ -3942,25 +3931,25 @@
     <row r="97" ht="48" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>神丶压制准备</t>
+          <t>霜降</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>先古</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>从抽牌堆或弃牌堆抽尽可能多的攻击牌。；获得2/5层活力。；灵感：优先抽灵感牌。</t>
+          <t>你的打击牌也可以触发灵感。；其灵感效果：费用减少1。</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -3970,7 +3959,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHEN_YA_ZHI_ZHUN_BEI；类: ShenYaZhiZhunBei；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-SHUANG_JIANG；类: ShuangJiang；牌池: 无卡池；源码关键词: Innate</t>
         </is>
       </c>
       <c r="H97" s="2" t="n"/>
@@ -3978,7 +3967,7 @@
     <row r="98" ht="48" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>天际斩击</t>
+          <t>上弦之月</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
@@ -3986,7 +3975,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>先古</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3996,7 +3985,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，将手中所有牌放到抽牌堆顶部，并抽出那个数量+2的牌。</t>
+          <t>当你打出的月影单次命中伤害达到50或更高时，将1张居合加入手中。</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -4006,7 +3995,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_JI_ZHAN_JI；类: TianJiZhanJi；牌池: 主牌池；源码关键词: Innate</t>
+          <t>ID: YUKIMOD-SHANG_XIAN_ZHI_YUE；类: ShangXianZhiYue；牌池: 无卡池</t>
         </is>
       </c>
       <c r="H98" s="2" t="n"/>
@@ -4032,7 +4021,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害。；其他攻击命中时，本牌伤害+1/2（当前造成{CurrentDamage}点伤害）。</t>
+          <t>造成5点伤害。；其他攻击命中时，本牌伤害+1/2。</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -4240,10 +4229,19 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="11"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4316,13 +4314,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1</v>
@@ -4353,10 +4351,10 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -4390,10 +4388,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>6</v>
@@ -4427,13 +4425,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>16</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>13</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1</v>
@@ -4464,10 +4462,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="9"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4555,25 +4560,25 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>18</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
@@ -4586,28 +4591,28 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>10</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -4617,10 +4622,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -4629,16 +4634,16 @@
         <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4716,10 +4721,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="12"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4797,13 +4812,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -4837,10 +4852,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>10</v>
@@ -4880,10 +4895,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
@@ -4917,7 +4932,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
@@ -5020,7 +5035,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>

--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -2,6 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卡牌表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="流派统计" sheetId="2" state="visible" r:id="rId2"/>
@@ -10,7 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键词，能力与遗物" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'卡牌表'!$A$1:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'流派统计'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'稀有度统计'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'种类统计'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'说明'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'关键词，能力与遗物'!$A$1:$C$5</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,8 +32,10 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -36,24 +50,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </left>
       <right style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </right>
       <top style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD6DEE6"/>
+        <color rgb="00D6DEE6"/>
       </bottom>
     </border>
   </borders>
@@ -70,8 +90,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -144,7 +165,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -186,14 +207,72 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -201,15 +280,55 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -218,13 +337,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -258,13 +377,24 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -290,7 +420,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -312,6 +442,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -613,7 +745,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>造成4/5点伤害3次。；灵感：这张牌费用减少1。</t>
+          <t>造成3/4点伤害3次。；灵感：这张牌费用减少1。；黑云：抽1张牌。</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -685,7 +817,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>造成8/10点伤害。；{IfUpgraded:show:选择1张牌触发灵感。\|随机1张牌触发灵感。}</t>
+          <t>造成8/10点伤害。；{IfUpgraded:show:选择1张牌触发灵感。|随机1张牌触发灵感。}</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -721,7 +853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；获得1层雪。；灵感：抽1张牌。</t>
+          <t>造成6/8点伤害。；获得1层雪。；灵感：抽1张牌。</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -739,7 +871,7 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>一现</t>
+          <t>天眼</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -757,7 +889,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>抽2/3张牌。；灵感：抽1张牌。</t>
+          <t>获得7/9点格挡。；预见3/5。</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -767,7 +899,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YI_XIAN；类: YiXian；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TIAN_YAN；类: TianYan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
@@ -775,7 +907,7 @@
     <row r="13" ht="48" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>天眼</t>
+          <t>月光</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -793,17 +925,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>获得7/9点格挡。；预见3/5。</t>
+          <t>凝聚1。</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_YAN；类: TianYan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YUE_GUANG；类: YueGuang；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H13" s="2" t="n"/>
@@ -811,7 +943,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>月光</t>
+          <t>花</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -824,22 +956,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>凝聚1。</t>
+          <t>造成6/8点伤害。；获得1层花。；黑云：减少1费。</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YUE_GUANG；类: YueGuang；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-HUA；类: Hua；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H14" s="2" t="n"/>
@@ -847,7 +979,7 @@
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>花</t>
+          <t>黑云奥义：影</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -865,7 +997,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；获得1层花。；黑云：额外攻击1次。</t>
+          <t>造成4/5点伤害2次。；黑云：额外攻击2次；否则，获得2层无明。</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -875,7 +1007,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUA；类: Hua；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YING_FU；类: HeiYunMiFaYingFu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H15" s="2" t="n"/>
@@ -883,7 +1015,7 @@
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：影</t>
+          <t>黑云奥义：灭</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -901,7 +1033,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>造成4/5点伤害2次。；黑云：额外攻击2次；否则，获得2层无明。</t>
+          <t>造成9/12点伤害。；黑云：额外攻击1次；否则，施加1层虚弱。</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -911,7 +1043,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YING_FU；类: HeiYunMiFaYingFu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_MIE；类: HeiYunAoYiMie；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H16" s="2" t="n"/>
@@ -919,7 +1051,7 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：灭</t>
+          <t>黑云秘法：积雨</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -932,12 +1064,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；黑云：额外攻击1次；否则，施加1层虚弱。</t>
+          <t>获得8/11点格挡。；在你的下回合开始时，进入黑云姿态。</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -947,7 +1079,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_MIE；类: HeiYunAoYiMie；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JI_YU；类: HeiYunMiFaJiYu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H17" s="2" t="n"/>
@@ -955,7 +1087,7 @@
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：积雨</t>
+          <t>黑云秘法：黄昏</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -973,7 +1105,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>获得8/11点格挡。；在你的下回合开始时，进入黑云姿态。</t>
+          <t>获得8/10点格挡。；获得2/3层无明。</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -983,7 +1115,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JI_YU；类: HeiYunMiFaJiYu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_HUANG_HUN；类: HeiYunMiFaHuangHun；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H18" s="2" t="n"/>
@@ -1019,7 +1151,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-DAO_QIAO_DA_JI；类: DaoQiaoDaJi；牌池: 主牌池；升级能量变化: +1</t>
+          <t>ID: YUKIMOD-DAO_QIAO_DA_JI；类: DaoQiaoDaJi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H19" s="2" t="n"/>
@@ -1027,7 +1159,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：黄昏</t>
+          <t>明镜止水</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1040,22 +1172,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>获得8/10点格挡。；获得2/3层无明。</t>
+          <t>造成9/12点伤害。；你的下一张攻击牌费用减少1。</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_HUANG_HUN；类: HeiYunMiFaHuangHun；牌池: 主牌池；沿用斩钢闪卡图</t>
+          <t>ID: YUKIMOD-YI_SHI；类: YiShi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H20" s="2" t="n"/>
@@ -1081,7 +1213,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；获得1层月。；你手中的月影伤害+3。</t>
+          <t>造成6/8点伤害。；额外攻击1次。；获得1层月。</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1243,11 +1375,11 @@
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>严寒</t>
+          <t>一现</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1261,7 +1393,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>造成8/11点伤害。；抽1张牌。；灵感：额外释放1次。</t>
+          <t>造成4/7点伤害。；灵感：获得1。</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1271,7 +1403,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YAN_HAN；类: YanHan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YI_XIAN；类: YiXian；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H26" s="2" t="n"/>
@@ -1279,7 +1411,7 @@
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>冰雪</t>
+          <t>严寒</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -1297,7 +1429,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>造成4点伤害2/3次。；抽1张牌，优先抽灵感牌。</t>
+          <t>造成8/11点伤害。；抽1张牌。；灵感：额外释放1次。</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1307,7 +1439,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BING_XUE；类: BingXue；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YAN_HAN；类: YanHan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H27" s="2" t="n"/>
@@ -1315,7 +1447,7 @@
     <row r="28" ht="48" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>破冰斩</t>
+          <t>冰雪</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -1333,7 +1465,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>选择1张手牌消耗。；对所有敌人造成7/10点伤害。；灵感：额外攻击一次。</t>
+          <t>造成4点伤害2/3次。；抽1张牌，优先抽灵感牌。</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1343,7 +1475,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-PO_BING_ZHAN；类: PoBingZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BING_XUE；类: BingXue；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H28" s="2" t="n"/>
@@ -1351,11 +1483,11 @@
     <row r="29" ht="48" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>高速斩击</t>
+          <t>破冰斩</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -1369,7 +1501,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成12/15点伤害。；抽2/3张牌。；灵感：这张牌费用减少1。</t>
+          <t>选择1张手牌消耗。；对所有敌人造成7/10点伤害。；灵感：额外攻击一次。</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1379,7 +1511,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-GAO_SU_ZHAN_JI；类: GaoSuZhanJi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-PO_BING_ZHAN；类: PoBingZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H29" s="2" t="n"/>
@@ -1387,11 +1519,11 @@
     <row r="30" ht="48" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>命定</t>
+          <t>高速斩击</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -1400,12 +1532,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>预见3/5。；抽2张牌。</t>
+          <t>对所有敌人造成12/15点伤害。；抽2/3张牌。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1415,7 +1547,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-MING_DING；类: MingDing；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-GAO_SU_ZHAN_JI；类: GaoSuZhanJi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H30" s="2" t="n"/>
@@ -1423,11 +1555,11 @@
     <row r="31" ht="48" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>天际</t>
+          <t>命定</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -1441,7 +1573,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>把你的手牌放到抽牌堆顶部。；抽等量的牌。；灵感：抽1张牌。</t>
+          <t>预见3/5。；抽2张牌。</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1451,7 +1583,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_JI；类: TianJi；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-MING_DING；类: MingDing；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H31" s="2" t="n"/>
@@ -1459,11 +1591,11 @@
     <row r="32" ht="48" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>寒冰庇护</t>
+          <t>天际</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -1477,7 +1609,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>获得12/16点格挡。；在你的下回合开始时，抽2张牌。；灵感：这张牌费用减少1。</t>
+          <t>把你的手牌放到抽牌堆顶部。；抽等量的牌。；灵感：抽1张牌。</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1487,7 +1619,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HAN_BING_BI_HU；类: HanBingBiHu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-TIAN_JI；类: TianJi；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H32" s="2" t="n"/>
@@ -1495,11 +1627,11 @@
     <row r="33" ht="48" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>灵光</t>
+          <t>寒冰庇护</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -1513,7 +1645,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>抽2/3张牌。</t>
+          <t>获得12/16点格挡。；在你的下回合开始时，抽2张牌。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1523,7 +1655,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LING_GUANG；类: LingGuang；牌池: 主牌池；源码关键词: Exhaust</t>
+          <t>ID: YUKIMOD-HAN_BING_BI_HU；类: HanBingBiHu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H33" s="2" t="n"/>
@@ -1531,7 +1663,7 @@
     <row r="34" ht="48" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>先见之明</t>
+          <t>拔刀斩</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -1544,12 +1676,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，预见3/4。</t>
+          <t>抽1张牌并打出。；灵感：这张牌费用减少1。</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1559,7 +1691,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-XIAN_JIAN_ZHI_MING；类: XianJianZhiMing；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BA_DAO_ZHAN；类: BaDaoZhan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H34" s="2" t="n"/>
@@ -1567,11 +1699,11 @@
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>冰点之刃</t>
+          <t>灵光</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -1580,12 +1712,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>当灵感触发时，对随机敌人造成4/6点伤害。</t>
+          <t>抽2/3张牌。</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1595,7 +1727,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BING_DIAN_ZHI_REN；类: BingDianZhiRen；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-LING_GUANG；类: LingGuang；牌池: 主牌池；源码关键词: Exhaust</t>
         </is>
       </c>
       <c r="H35" s="2" t="n"/>
@@ -1603,7 +1735,7 @@
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>咒术</t>
+          <t>先见之明</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -1616,22 +1748,22 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>升级你手中的月影。；你手中的月影伤害+5。</t>
+          <t>回合开始时，预见3/4。</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-ZHOU_SHU；类: ZhouShu；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-XIAN_JIAN_ZHI_MING；类: XianJianZhiMing；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H36" s="2" t="n"/>
@@ -1639,11 +1771,11 @@
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>圆舞</t>
+          <t>冰点之刃</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -1652,22 +1784,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>获得12/16点格挡。；凝聚1。</t>
+          <t>当灵感触发时，对随机敌人造成4/6点伤害。</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>月影</t>
+          <t>灵感</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YUAN_WU；类: YuanWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BING_DIAN_ZHI_REN；类: BingDianZhiRen；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H37" s="2" t="n"/>
@@ -1675,7 +1807,7 @@
     <row r="38" ht="48" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>拨云见日</t>
+          <t>咒术</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -1693,17 +1825,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>获得3/4层无明。；在你的下回合开始时，进入黑云姿态。</t>
+          <t>升级你手中的月影。；你手中的月影伤害+5。</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BO_RI_JIAN_YUN；类: BoRiJianYun；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-ZHOU_SHU；类: ZhouShu；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H38" s="2" t="n"/>
@@ -1711,11 +1843,11 @@
     <row r="39" ht="48" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：残</t>
+          <t>圆舞</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -1729,17 +1861,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>抽1张牌。；进入黑云姿态。</t>
+          <t>获得12/16点格挡。；凝聚1。；选择1张手牌消耗。</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>月影</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_CAN；类: HeiYunAoYiCan；牌池: 主牌池；升级获得保留</t>
+          <t>ID: YUKIMOD-YUAN_WU；类: YuanWu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H39" s="2" t="n"/>
@@ -1747,7 +1879,7 @@
     <row r="40" ht="48" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：降临</t>
+          <t>拨云见日</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -1765,7 +1897,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>获得9/12点格挡。；下次进入黑云姿态时，对所有敌人施加1层易伤。</t>
+          <t>获得3/4层无明。；在你的下回合开始时，进入黑云姿态。；选择1张手牌保留1回合。</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1775,7 +1907,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JIANG_LIN；类: HeiYunMiFaJiangLin；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BO_RI_JIAN_YUN；类: BoRiJianYun；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H40" s="2" t="n"/>
@@ -1783,11 +1915,11 @@
     <row r="41" ht="48" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：魂佑</t>
+          <t>黑云奥义：残</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -1801,7 +1933,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>获得12点格挡。；黑云：获得12点格挡；否则，下次进入黑云姿态时获得1/2。</t>
+          <t>抽1张牌。；进入黑云姿态。；选择1张手牌消耗。</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -1811,7 +1943,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_HUN_YOU；类: HeiYunMiFaHunYou；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_CAN；类: HeiYunAoYiCan；牌池: 主牌池；源码关键词: Retain</t>
         </is>
       </c>
       <c r="H41" s="2" t="n"/>
@@ -1819,7 +1951,7 @@
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>威压</t>
+          <t>黑云秘法：降临</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -1832,12 +1964,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>黑云姿态时，攻击命中获得2/3点格挡。</t>
+          <t>获得9/12点格挡。；下次进入黑云姿态时，对所有敌人施加1层易伤。</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -1847,7 +1979,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-WEI_YA；类: WeiYa；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_JIANG_LIN；类: HeiYunMiFaJiangLin；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H42" s="2" t="n"/>
@@ -1855,11 +1987,11 @@
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>剑舞</t>
+          <t>黑云秘法：魂佑</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -1868,22 +2000,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>根据本回合额外抽牌的数量造成5/7点伤害（当前{CurrentHitCount}次）。</t>
+          <t>获得12点格挡。；黑云：获得12点格挡；否则，下次进入黑云姿态时获得1/2。</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-JIAN_WU；类: JianWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_HUN_YOU；类: HeiYunMiFaHunYou；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H43" s="2" t="n"/>
@@ -1891,7 +2023,7 @@
     <row r="44" ht="48" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>妖怪狩猎</t>
+          <t>威压</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -1904,22 +2036,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>造成2点伤害2/3次。；凝聚1。</t>
+          <t>处于黑云姿态时，你的攻击命中会获得2/3点格挡。</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YAO_GUAI_SHOU_LIE；类: YaoGuaiShouLie；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-WEI_YA；类: WeiYa；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H44" s="2" t="n"/>
@@ -1927,7 +2059,7 @@
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>幻变斩</t>
+          <t>剑舞</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -1945,7 +2077,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>造成3点伤害2/3次。；消耗1张手牌。；抽1张牌。</t>
+          <t>根据本回合额外抽牌的数量造成5/7点伤害（当前{CurrentHitCount}次）。</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -1955,7 +2087,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HUAN_BIAN_ZHAN；类: HuanBianZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-JIAN_WU；类: JianWu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H45" s="2" t="n"/>
@@ -1963,15 +2095,15 @@
     <row r="46" ht="48" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>影月</t>
+          <t>妖怪狩猎</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
+          <t>罕见</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1981,7 +2113,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>造成5/10点伤害。；这张牌视为月影。；每当你使用其他攻击命中时，这张牌伤害+1。</t>
+          <t>造成2点伤害2/3次。；凝聚1。</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1991,7 +2123,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHADOW_MOON；类: ShadowMoon；牌池: 主牌池；源码关键词: Retain, Exhaust</t>
+          <t>ID: YUKIMOD-YAO_GUAI_SHOU_LIE；类: YaoGuaiShouLie；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H46" s="2" t="n"/>
@@ -1999,7 +2131,7 @@
     <row r="47" ht="48" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>彼岸花</t>
+          <t>幻变斩</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -2017,7 +2149,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>造成6/9点伤害。\n在接下来的2个回合开始时，造成6/9点伤害。</t>
+          <t>造成3点伤害2/3次。；消耗1张手牌。；抽1张牌。</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2027,7 +2159,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BI_AN_HUA；类: BiAnHua；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HUAN_BIAN_ZHAN；类: HuanBianZhan；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H47" s="2" t="n"/>
@@ -2035,7 +2167,7 @@
     <row r="48" ht="48" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>明镜止水</t>
+          <t>彼岸花</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
@@ -2053,7 +2185,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；你的下一张攻击牌费用减少1。</t>
+          <t>造成6/9点伤害。\n在接下来的2个回合开始时，造成6/9点伤害。</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2063,7 +2195,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YI_SHI；类: YiShi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-BI_AN_HUA；类: BiAnHua；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H48" s="2" t="n"/>
@@ -2071,11 +2203,11 @@
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>踏前斩</t>
+          <t>看破</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
@@ -2089,7 +2221,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>造成2/3点伤害。；对这回合没被踏前斩命中的敌人释放时返回手牌。</t>
+          <t>造成9/12点伤害。；将抽牌堆中的1张牌放入你的手牌。</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2099,7 +2231,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TA_QIAN_ZHAN；类: TaQianZhan；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-KAN_PO；类: KanPo；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H49" s="2" t="n"/>
@@ -2125,7 +2257,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害3/4次。\n每次抽到时，费用在本场战斗中减少1。</t>
+          <t>对所有敌人造成5点伤害3/4次。\n每次加入手牌时，费用在本场战斗中减少1。</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2359,11 +2491,11 @@
     <row r="57" ht="48" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>怒涛斩</t>
+          <t>踏前斩</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -2372,12 +2504,12 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>一回合内首次打出3张攻击牌时，获得1。</t>
+          <t>选择1名队友。；该队友凝聚1。</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2387,7 +2519,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-NU_TAO_ZHAN；类: NuTaoZhan；牌池: 主牌池；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-TA_QIAN_ZHAN；类: TaQianZhan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H57" s="2" t="n"/>
@@ -2539,7 +2671,7 @@
     <row r="62" ht="48" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>拔刀斩</t>
+          <t>寒霜</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -2547,17 +2679,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>罕见</t>
+          <t>稀有</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>抽1张牌并打出。；灵感：这张牌费用减少1。</t>
+          <t>回合开始时，随机触发1/2张手中的灵感。</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2567,7 +2699,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-BA_DAO_ZHAN；类: BaDaoZhan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-HAN_SHUANG；类: HanShuang；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H62" s="2" t="n"/>
@@ -2575,7 +2707,7 @@
     <row r="63" ht="48" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>雪影</t>
+          <t>沉思</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -2588,12 +2720,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>抽2张牌。；灵感：这张牌费用减少1。</t>
+          <t>当灵感触发时，获得2/3点格挡。</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2603,7 +2735,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-XUE_YING；类: XueYing；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-CHEN_SI；类: ChenSi；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H63" s="2" t="n"/>
@@ -2611,7 +2743,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>寒霜</t>
+          <t>瞬念</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -2629,7 +2761,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，随机触发1/2张手中的灵感。</t>
+          <t>回合开始时，将1张随机的{IfUpgraded:show:升级过的}灵感牌加入手中。</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2639,7 +2771,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HAN_SHUANG；类: HanShuang；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-SHUN_NIAN；类: ShunNian；牌池: 主牌池；源码关键词: Exhaust</t>
         </is>
       </c>
       <c r="H64" s="2" t="n"/>
@@ -2647,7 +2779,7 @@
     <row r="65" ht="48" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>沉思</t>
+          <t>零度</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -2665,7 +2797,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>当灵感触发时，获得2/3点格挡。</t>
+          <t>当你触发12/9次灵感时，将1张居合加入手中。</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -2675,7 +2807,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-CHEN_SI；类: ChenSi；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-LING_DU；类: LingDu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H65" s="2" t="n"/>
@@ -2683,7 +2815,7 @@
     <row r="66" ht="48" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>零度</t>
+          <t>黑云奥义：黑雾</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -2696,22 +2828,22 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>当你触发12/9次灵感时，将1张居合加入手中。</t>
+          <t>造成8/10点伤害。；黑云：消耗手牌中所有非黑云的牌，每消耗1张，额外攻击1次；否则，获得2/3层无明。</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>灵感</t>
+          <t>黑云</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-LING_DU；类: LingDu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_AO_YI_HEI_WU；类: HeiYunAoYiHeiWu；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H66" s="2" t="n"/>
@@ -2719,11 +2851,11 @@
     <row r="67" ht="48" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>黑云奥义：黑雾</t>
+          <t>黑云心法</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
@@ -2732,12 +2864,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>造成8/10点伤害。；黑云：你手中每有1张技能牌，额外攻击1次；否则，获得3层无明。</t>
+          <t>本回合内保留黑云姿态。</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2747,7 +2879,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_AO_YI_HEI_WU；类: HeiYunAoYiHeiWu；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_XIN_FA；类: HeiYunXinFa；牌池: 主牌池；源码关键词: Retain</t>
         </is>
       </c>
       <c r="H67" s="2" t="n"/>
@@ -2755,11 +2887,11 @@
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>黑云心法</t>
+          <t>黑云秘法：幕临</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
@@ -2773,7 +2905,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>本回合内保留黑云姿态。升级：获得保留。</t>
+          <t>黑云：获得2，抽2张牌；否则，下次进入黑云姿态时获得{DelayedEnergy:energyIcons()}，抽2张牌。</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -2783,7 +2915,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_XIN_FA；类: HeiYunXinFa；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_MU_LIN；类: HeiYunMiFaMuLin；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H68" s="2" t="n"/>
@@ -2791,11 +2923,11 @@
     <row r="69" ht="48" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：出鞘</t>
+          <t>黑云秘法：燕返</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
@@ -2809,7 +2941,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>进入黑云姿态。；下次退出黑云姿态时，将1张{IfUpgraded:show:纳刀+|纳刀}加入手中。</t>
+          <t>黑云：释放你上一次释放的黑云牌（自身除外）。否则，你下一张释放的黑云牌（自身除外）额外释放一次。</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -2819,7 +2951,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_CHU_QIAO；类: HeiYunMiFaChuQiao；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YAN_HUI；类: HeiYunMiFaYanHui；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H69" s="2" t="n"/>
@@ -2827,11 +2959,11 @@
     <row r="70" ht="48" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：幕临</t>
+          <t>漫天</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
@@ -2840,12 +2972,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>黑云：获得2点能量，抽2张牌；否则，下次进入黑云姿态时获得2点能量，抽2张牌。</t>
+          <t>处于黑云姿态时，每当你使用黑云牌，抽1张牌。</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -2855,7 +2987,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_MU_LIN；类: HeiYunMiFaMuLin；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-MAN_TIAN；类: ManTian；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H70" s="2" t="n"/>
@@ -2863,7 +2995,7 @@
     <row r="71" ht="48" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>黑云秘法：燕返</t>
+          <t>黑云秘法：出鞘</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
@@ -2876,12 +3008,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>黑云：释放你上一次释放的黑云牌。否则，你下一张释放的黑云牌额外释放一次。</t>
+          <t>每当你进入黑云姿态时，将1张{IfUpgraded:show:升级过的}具有虚无的随机黑云牌加入手中。</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -2891,7 +3023,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HEI_YUN_MI_FA_YAN_HUI；类: HeiYunMiFaYanHui；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-HEI_YUN_MI_FA_CHU_QIAO；类: HeiYunMiFaChuQiao；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H71" s="2" t="n"/>
@@ -2971,11 +3103,11 @@
     <row r="74" ht="48" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>燕回反</t>
+          <t>影月</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
@@ -2989,7 +3121,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>释放你上一个释放的攻击1次。</t>
+          <t>造成5/10点伤害。；这张牌视为月影。；每当你使用其他攻击命中时，这张牌伤害+1。</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -2999,7 +3131,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-YAN_HUI_FAN；类: YanHuiFan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-SHADOW_MOON；类: ShadowMoon；牌池: 主牌池；源码关键词: Retain, Exhaust</t>
         </is>
       </c>
       <c r="H74" s="2" t="n"/>
@@ -3007,11 +3139,11 @@
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>看破</t>
+          <t>燕回反</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
@@ -3025,7 +3157,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>造成9/12点伤害。；将抽牌堆中的1张牌放入你的手牌。</t>
+          <t>释放你上一个释放的攻击1次。</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3035,7 +3167,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-KAN_PO；类: KanPo；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-YAN_HUI_FAN；类: YanHuiFan；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
         </is>
       </c>
       <c r="H75" s="2" t="n"/>
@@ -3119,7 +3251,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
@@ -3169,7 +3301,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>本回合内，你的攻击命中时，手中月影伤害+2/3。</t>
+          <t>本回合内，你的攻击命中时，手中月影伤害+3/4。</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3215,7 +3347,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-CAN_YUE；类: CanYue；牌池: 主牌池；源码关键词: Exhaust；升级移除消耗</t>
+          <t>ID: YUKIMOD-CAN_YUE；类: CanYue；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H80" s="2" t="n"/>
@@ -3223,11 +3355,11 @@
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>红尘</t>
+          <t>天刀形态</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
@@ -3241,7 +3373,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>使用灵感卡时，随机1张手牌下次使用前费用减少1。</t>
+          <t>回合结束时，释放你本回合首次使用的攻击牌。；回合开始时，释放你上回合最后使用的技能牌。</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3251,7 +3383,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-HONG_CHEN；类: HongChen；牌池: 主牌池；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-TIAN_DAO_XING_TAI；类: TianDaoXingTai；牌池: 主牌池；源码关键词: Retain</t>
         </is>
       </c>
       <c r="H81" s="2" t="n"/>
@@ -3259,11 +3391,11 @@
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>天刀形态</t>
+          <t>怒涛斩</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
@@ -3277,7 +3409,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>回合结束释放你本回合首次使用的攻击牌。；回合开始时释放上回合最后使用的技能牌。</t>
+          <t>每打出4张攻击牌，获得1。</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -3287,7 +3419,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_DAO_XING_TAI；类: TianDaoXingTai；牌池: 主牌池；升级获得保留</t>
+          <t>ID: YUKIMOD-NU_TAO_ZHAN；类: NuTaoZhan；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H82" s="2" t="n"/>
@@ -3367,7 +3499,7 @@
     <row r="85" ht="48" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>漫天</t>
+          <t>红尘</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
@@ -3385,17 +3517,17 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>黑云姿态使用黑云牌时抽1张牌。</t>
+          <t>每当你使用灵感牌时，随机1张手牌下次使用前费用减少1。</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>黑云</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-MAN_TIAN；类: ManTian；牌池: 主牌池；升级费用变化: -1</t>
+          <t>ID: YUKIMOD-HONG_CHEN；类: HongChen；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H85" s="2" t="n"/>
@@ -3403,7 +3535,7 @@
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>瞬念</t>
+          <t>雪影</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
@@ -3421,7 +3553,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，将1张随机的{IfUpgraded:show:升级过的}灵感牌加入手中。</t>
+          <t>所有队友获得：打出33张牌时，将1张居合加入手中。</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3431,7 +3563,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHUN_NIAN；类: ShunNian；牌池: 主牌池</t>
+          <t>ID: YUKIMOD-XUE_YING；类: XueYing；牌池: 主牌池；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H86" s="2" t="n"/>
@@ -3529,7 +3661,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，将手中所有牌放到抽牌堆顶部，并抽出那个数量+2的牌。</t>
+          <t>消耗抽牌堆和弃牌堆。；丢弃所有手牌，抽等量的牌。</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -3539,7 +3671,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-TIAN_JI_ZHAN_JI；类: TianJiZhanJi；牌池: 主牌池；源码关键词: Innate</t>
+          <t>ID: YUKIMOD-TIAN_JI_ZHAN_JI；类: TianJiZhanJi；牌池: 主牌池；源码关键词: Exhaust；升级费用变化: -1</t>
         </is>
       </c>
       <c r="H89" s="2" t="n"/>
@@ -4085,7 +4217,8 @@
       <c r="H104" s="2" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:H104"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4181,10 +4314,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>5</v>
@@ -4196,13 +4329,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -4249,7 +4382,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1</v>
@@ -4261,7 +4394,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
@@ -4273,10 +4406,10 @@
         <v>7</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -4286,19 +4419,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1</v>
@@ -4307,7 +4440,7 @@
         <v>4</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>16</v>
@@ -4317,7 +4450,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:K5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4429,7 +4563,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>1</v>
@@ -4438,13 +4572,13 @@
         <v>7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
@@ -4460,7 +4594,7 @@
         <v>41</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2</v>
@@ -4469,16 +4603,16 @@
         <v>8</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>11</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -4497,19 +4631,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>7</v>
-      </c>
       <c r="H5" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -4575,7 +4709,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:I7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4677,13 +4812,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -4692,7 +4827,7 @@
         <v>6</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1</v>
@@ -4701,7 +4836,7 @@
         <v>7</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -4711,19 +4846,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
@@ -4732,13 +4867,13 @@
         <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>16</v>
@@ -4751,7 +4886,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>0</v>
@@ -4760,10 +4895,10 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
@@ -4772,20 +4907,21 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:L4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4887,7 +5023,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4991,6 +5128,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:C5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/yuki-card-table.xlsx
+++ b/docs/yuki-card-table.xlsx
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>回合开始时，将1张随机的{IfUpgraded:show:升级过的}灵感牌加入手中。</t>
+          <t>回合开始时，将1张随机的{IfUpgraded:show:升级过的}灵感牌加入手中。它获得消耗。</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>ID: YUKIMOD-SHUN_NIAN；类: ShunNian；牌池: 主牌池；源码关键词: Exhaust</t>
+          <t>ID: YUKIMOD-SHUN_NIAN；类: ShunNian；牌池: 主牌池</t>
         </is>
       </c>
       <c r="H64" s="2" t="n"/>
